--- a/gstdatabase/GSTR-3B-2021-2022.xlsx
+++ b/gstdatabase/GSTR-3B-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91B4865-C668-4261-9515-E0B3783D669D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590B0E6C-E846-4FB4-91AA-E24715EFC665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,6 +447,12 @@
     <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -454,19 +460,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -768,13 +768,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -848,10 +848,10 @@
       <c r="AK2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="35"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -928,11 +928,11 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1072,10 +1072,10 @@
       <c r="BJ7" s="4"/>
     </row>
     <row r="8" spans="1:64" s="24" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="33" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="27">
@@ -1085,69 +1085,69 @@
       <c r="E8" s="28"/>
       <c r="F8" s="28"/>
       <c r="G8" s="29"/>
-      <c r="H8" s="30">
+      <c r="H8" s="32">
         <v>44317</v>
       </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="33">
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="30">
         <v>44348</v>
       </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="30">
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="32">
         <v>44378</v>
       </c>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="30">
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="32">
         <v>44409</v>
       </c>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="33">
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="30">
         <v>44440</v>
       </c>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="30">
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="32">
         <v>44470</v>
       </c>
-      <c r="AH8" s="31"/>
-      <c r="AI8" s="31"/>
-      <c r="AJ8" s="31"/>
-      <c r="AK8" s="31"/>
-      <c r="AL8" s="30">
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="32">
         <v>44501</v>
       </c>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="31"/>
-      <c r="AO8" s="31"/>
-      <c r="AP8" s="31"/>
-      <c r="AQ8" s="30">
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="32">
         <v>44531</v>
       </c>
-      <c r="AR8" s="31"/>
-      <c r="AS8" s="31"/>
-      <c r="AT8" s="31"/>
-      <c r="AU8" s="31"/>
-      <c r="AV8" s="30">
+      <c r="AR8" s="33"/>
+      <c r="AS8" s="33"/>
+      <c r="AT8" s="33"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="32">
         <v>44562</v>
       </c>
-      <c r="AW8" s="31"/>
-      <c r="AX8" s="31"/>
-      <c r="AY8" s="31"/>
-      <c r="AZ8" s="31"/>
+      <c r="AW8" s="33"/>
+      <c r="AX8" s="33"/>
+      <c r="AY8" s="33"/>
+      <c r="AZ8" s="33"/>
       <c r="BA8" s="27">
         <v>44593</v>
       </c>
@@ -1163,9 +1163,9 @@
       <c r="BI8" s="28"/>
       <c r="BJ8" s="29"/>
     </row>
-    <row r="9" spans="1:64" s="24" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="31"/>
+    <row r="9" spans="1:64" s="24" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="35"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="23" t="s">
         <v>3</v>
       </c>
@@ -1379,14 +1379,14 @@
       </c>
       <c r="J10" s="10">
         <f>K10-I10</f>
-        <v>42918</v>
+        <v>42919</v>
       </c>
       <c r="K10" s="20">
-        <v>56274</v>
+        <v>56275</v>
       </c>
       <c r="L10" s="12">
         <f>K10/H10</f>
-        <v>1.0426324273247736</v>
+        <v>1.0426509551071832</v>
       </c>
       <c r="M10" s="16">
         <v>85686</v>
@@ -1532,14 +1532,14 @@
       </c>
       <c r="BC10" s="10">
         <f>BD10-BB10</f>
-        <v>80220</v>
+        <v>14036</v>
       </c>
       <c r="BD10" s="20">
-        <v>132368</v>
+        <v>66184</v>
       </c>
       <c r="BE10" s="12">
         <f>BD10/BA10</f>
-        <v>2.0322724271874471</v>
+        <v>1.0161362135937235</v>
       </c>
       <c r="BF10" s="18">
         <v>104274</v>
@@ -1729,14 +1729,14 @@
       </c>
       <c r="AX11" s="10">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>9228</v>
+        <v>9229</v>
       </c>
       <c r="AY11" s="20">
-        <v>42503</v>
+        <v>42504</v>
       </c>
       <c r="AZ11" s="12">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.97021092037983925</v>
+        <v>0.97023374726077427</v>
       </c>
       <c r="BA11" s="18">
         <v>44164</v>
@@ -1746,14 +1746,14 @@
       </c>
       <c r="BC11" s="10">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>52420</v>
+        <v>9295</v>
       </c>
       <c r="BD11" s="20">
-        <v>86254</v>
+        <v>43129</v>
       </c>
       <c r="BE11" s="12">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>1.9530386740331491</v>
+        <v>0.9765646227696767</v>
       </c>
       <c r="BF11" s="18">
         <v>97423</v>
@@ -1763,14 +1763,14 @@
       </c>
       <c r="BH11" s="10">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>21909</v>
+        <v>21912</v>
       </c>
       <c r="BI11" s="11">
-        <v>95309</v>
+        <v>95312</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.97830081192326246</v>
+        <v>0.97833160547304021</v>
       </c>
       <c r="BK11" s="24"/>
       <c r="BL11" s="24"/>
@@ -1790,14 +1790,14 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" si="0"/>
-        <v>115334</v>
+        <v>115335</v>
       </c>
       <c r="F12" s="20">
-        <v>150925</v>
+        <v>150926</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="1"/>
-        <v>0.94057122914602298</v>
+        <v>0.94057746118994645</v>
       </c>
       <c r="H12" s="15">
         <v>161190</v>
@@ -1807,14 +1807,14 @@
       </c>
       <c r="J12" s="10">
         <f t="shared" si="2"/>
-        <v>115785</v>
+        <v>115787</v>
       </c>
       <c r="K12" s="20">
-        <v>152281</v>
+        <v>152283</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="3"/>
-        <v>0.94472982194925248</v>
+        <v>0.94474222966685273</v>
       </c>
       <c r="M12" s="16">
         <v>320319</v>
@@ -1824,14 +1824,14 @@
       </c>
       <c r="O12" s="10">
         <f t="shared" si="4"/>
-        <v>71877</v>
+        <v>71879</v>
       </c>
       <c r="P12" s="13">
-        <v>310313</v>
+        <v>310315</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="5"/>
-        <v>0.96876238999247621</v>
+        <v>0.96876863376821232</v>
       </c>
       <c r="R12" s="16">
         <v>159828</v>
@@ -1841,14 +1841,14 @@
       </c>
       <c r="T12" s="10">
         <f t="shared" si="6"/>
-        <v>27545</v>
+        <v>27547</v>
       </c>
       <c r="U12" s="20">
-        <v>150743</v>
+        <v>150745</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="7"/>
-        <v>0.94315764446780292</v>
+        <v>0.94317015791976377</v>
       </c>
       <c r="W12" s="16">
         <v>162180</v>
@@ -1858,14 +1858,14 @@
       </c>
       <c r="Y12" s="10">
         <f t="shared" si="8"/>
-        <v>30531</v>
+        <v>30533</v>
       </c>
       <c r="Z12" s="20">
-        <v>153696</v>
+        <v>153698</v>
       </c>
       <c r="AA12" s="12">
         <f t="shared" si="9"/>
-        <v>0.94768775434702179</v>
+        <v>0.94770008632383773</v>
       </c>
       <c r="AB12" s="17">
         <v>327297</v>
@@ -1875,14 +1875,14 @@
       </c>
       <c r="AD12" s="10">
         <f t="shared" si="10"/>
-        <v>52037</v>
+        <v>52039</v>
       </c>
       <c r="AE12" s="11">
-        <v>315591</v>
+        <v>315593</v>
       </c>
       <c r="AF12" s="12">
         <f t="shared" si="11"/>
-        <v>0.96423431928798609</v>
+        <v>0.9642404299458901</v>
       </c>
       <c r="AG12" s="16">
         <v>160729</v>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="AI12" s="10">
         <f t="shared" si="12"/>
-        <v>25209</v>
+        <v>25211</v>
       </c>
       <c r="AJ12" s="20">
-        <v>151380</v>
+        <v>151382</v>
       </c>
       <c r="AK12" s="12">
         <f t="shared" si="13"/>
-        <v>0.94183376988595713</v>
+        <v>0.94184621319114781</v>
       </c>
       <c r="AL12" s="18">
         <v>162572</v>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="AN12" s="10">
         <f t="shared" si="14"/>
-        <v>26348</v>
+        <v>26350</v>
       </c>
       <c r="AO12" s="11">
-        <v>153367</v>
+        <v>153369</v>
       </c>
       <c r="AP12" s="12">
         <f t="shared" si="15"/>
-        <v>0.94337893364170955</v>
+        <v>0.94339123588317797</v>
       </c>
       <c r="AQ12" s="11">
         <v>333129</v>
@@ -1926,14 +1926,14 @@
       </c>
       <c r="AS12" s="10">
         <f t="shared" si="16"/>
-        <v>49579</v>
+        <v>49581</v>
       </c>
       <c r="AT12" s="13">
-        <v>319719</v>
+        <v>319721</v>
       </c>
       <c r="AU12" s="12">
         <f t="shared" si="17"/>
-        <v>0.95974532388354061</v>
+        <v>0.95975132756379655</v>
       </c>
       <c r="AV12" s="18">
         <v>161987</v>
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AX12" s="10">
         <f t="shared" si="18"/>
-        <v>27156</v>
+        <v>27158</v>
       </c>
       <c r="AY12" s="20">
-        <v>152461</v>
+        <v>152463</v>
       </c>
       <c r="AZ12" s="12">
         <f t="shared" si="19"/>
-        <v>0.94119281176884562</v>
+        <v>0.94120515843864017</v>
       </c>
       <c r="BA12" s="18">
         <v>163270</v>
@@ -1960,14 +1960,14 @@
       </c>
       <c r="BC12" s="10">
         <f t="shared" si="20"/>
-        <v>182017</v>
+        <v>27500</v>
       </c>
       <c r="BD12" s="20">
-        <v>309038</v>
+        <v>154521</v>
       </c>
       <c r="BE12" s="12">
         <f t="shared" si="21"/>
-        <v>1.8928033319042077</v>
+        <v>0.94641391559992649</v>
       </c>
       <c r="BF12" s="18">
         <v>336608</v>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="BH12" s="10">
         <f t="shared" si="22"/>
-        <v>63225</v>
+        <v>63227</v>
       </c>
       <c r="BI12" s="11">
-        <v>323426</v>
+        <v>323428</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="23"/>
-        <v>0.96083872041068541</v>
+        <v>0.96084466204011787</v>
       </c>
       <c r="BK12" s="24"/>
       <c r="BL12" s="24"/>
@@ -2174,14 +2174,14 @@
       </c>
       <c r="BC13" s="10">
         <f t="shared" si="20"/>
-        <v>18450</v>
+        <v>2773</v>
       </c>
       <c r="BD13" s="20">
-        <v>31354</v>
+        <v>15677</v>
       </c>
       <c r="BE13" s="12">
         <f t="shared" si="21"/>
-        <v>1.9805445012949277</v>
+        <v>0.99027225064746383</v>
       </c>
       <c r="BF13" s="18">
         <v>27469</v>
@@ -2303,14 +2303,14 @@
       </c>
       <c r="AD14" s="10">
         <f t="shared" si="10"/>
-        <v>33624</v>
+        <v>33625</v>
       </c>
       <c r="AE14" s="11">
-        <v>139179</v>
+        <v>139180</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="11"/>
-        <v>0.96597076664677062</v>
+        <v>0.96597770713899034</v>
       </c>
       <c r="AG14" s="16">
         <v>79635</v>
@@ -2337,14 +2337,14 @@
       </c>
       <c r="AN14" s="10">
         <f t="shared" si="14"/>
-        <v>19068</v>
+        <v>19069</v>
       </c>
       <c r="AO14" s="11">
-        <v>76993</v>
+        <v>76994</v>
       </c>
       <c r="AP14" s="12">
         <f t="shared" si="15"/>
-        <v>0.94732632822304796</v>
+        <v>0.9473386322809263</v>
       </c>
       <c r="AQ14" s="11">
         <v>148266</v>
@@ -2354,14 +2354,14 @@
       </c>
       <c r="AS14" s="10">
         <f t="shared" si="16"/>
-        <v>30169</v>
+        <v>30171</v>
       </c>
       <c r="AT14" s="13">
-        <v>142664</v>
+        <v>142666</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="17"/>
-        <v>0.96221655672912199</v>
+        <v>0.96223004599840822</v>
       </c>
       <c r="AV14" s="18">
         <v>81291</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="BC14" s="10">
         <f t="shared" si="20"/>
-        <v>99069</v>
+        <v>20690</v>
       </c>
       <c r="BD14" s="20">
-        <v>156758</v>
+        <v>78379</v>
       </c>
       <c r="BE14" s="12">
         <f t="shared" si="21"/>
-        <v>1.9033499678237957</v>
+        <v>0.95167498391189786</v>
       </c>
       <c r="BF14" s="18">
         <v>151377</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="BH14" s="10">
         <f t="shared" si="22"/>
-        <v>36688</v>
+        <v>36689</v>
       </c>
       <c r="BI14" s="11">
-        <v>145238</v>
+        <v>145239</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.95944562251861243</v>
+        <v>0.95945222854198453</v>
       </c>
       <c r="BK14" s="24"/>
       <c r="BL14" s="24"/>
@@ -2534,14 +2534,14 @@
       </c>
       <c r="AI15" s="10">
         <f t="shared" si="12"/>
-        <v>53549</v>
+        <v>53550</v>
       </c>
       <c r="AJ15" s="20">
-        <v>245085</v>
+        <v>245086</v>
       </c>
       <c r="AK15" s="12">
         <f t="shared" si="13"/>
-        <v>0.93612494652569822</v>
+        <v>0.93612876611868234</v>
       </c>
       <c r="AL15" s="18">
         <v>265773</v>
@@ -2551,14 +2551,14 @@
       </c>
       <c r="AN15" s="10">
         <f t="shared" si="14"/>
-        <v>53421</v>
+        <v>53422</v>
       </c>
       <c r="AO15" s="11">
-        <v>248573</v>
+        <v>248574</v>
       </c>
       <c r="AP15" s="12">
         <f t="shared" si="15"/>
-        <v>0.93528311754768167</v>
+        <v>0.93528688015712658</v>
       </c>
       <c r="AQ15" s="11">
         <v>464263</v>
@@ -2568,14 +2568,14 @@
       </c>
       <c r="AS15" s="10">
         <f t="shared" si="16"/>
-        <v>80951</v>
+        <v>80952</v>
       </c>
       <c r="AT15" s="13">
-        <v>442066</v>
+        <v>442067</v>
       </c>
       <c r="AU15" s="12">
         <f t="shared" si="17"/>
-        <v>0.95218873784902092</v>
+        <v>0.95219089180055272</v>
       </c>
       <c r="AV15" s="18">
         <v>264802</v>
@@ -2585,14 +2585,14 @@
       </c>
       <c r="AX15" s="10">
         <f t="shared" si="18"/>
-        <v>52834</v>
+        <v>52835</v>
       </c>
       <c r="AY15" s="20">
-        <v>250497</v>
+        <v>250498</v>
       </c>
       <c r="AZ15" s="12">
         <f t="shared" si="19"/>
-        <v>0.9459785046940733</v>
+        <v>0.9459822811005959</v>
       </c>
       <c r="BA15" s="18">
         <v>267720</v>
@@ -2602,14 +2602,14 @@
       </c>
       <c r="BC15" s="10">
         <f t="shared" si="20"/>
-        <v>311422</v>
+        <v>56297</v>
       </c>
       <c r="BD15" s="20">
-        <v>510250</v>
+        <v>255125</v>
       </c>
       <c r="BE15" s="12">
         <f t="shared" si="21"/>
-        <v>1.9059091588226504</v>
+        <v>0.95295457941132522</v>
       </c>
       <c r="BF15" s="18">
         <v>469904</v>
@@ -2646,14 +2646,14 @@
       </c>
       <c r="E16" s="10">
         <f t="shared" si="0"/>
-        <v>313665</v>
+        <v>313666</v>
       </c>
       <c r="F16" s="20">
-        <v>373030</v>
+        <v>373031</v>
       </c>
       <c r="G16" s="12">
         <f t="shared" si="1"/>
-        <v>0.91758171478048689</v>
+        <v>0.91758417458724439</v>
       </c>
       <c r="H16" s="15">
         <v>404491</v>
@@ -2663,14 +2663,14 @@
       </c>
       <c r="J16" s="10">
         <f t="shared" si="2"/>
-        <v>285986</v>
+        <v>285987</v>
       </c>
       <c r="K16" s="20">
-        <v>369987</v>
+        <v>369988</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="3"/>
-        <v>0.91469773122269715</v>
+        <v>0.91470020346559011</v>
       </c>
       <c r="M16" s="16">
         <v>718779</v>
@@ -2680,14 +2680,14 @@
       </c>
       <c r="O16" s="10">
         <f t="shared" si="4"/>
-        <v>196841</v>
+        <v>196843</v>
       </c>
       <c r="P16" s="13">
-        <v>676520</v>
+        <v>676522</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="5"/>
-        <v>0.94120724172520343</v>
+        <v>0.94121002422163136</v>
       </c>
       <c r="R16" s="16">
         <v>403668</v>
@@ -2697,14 +2697,14 @@
       </c>
       <c r="T16" s="10">
         <f t="shared" si="6"/>
-        <v>91181</v>
+        <v>91182</v>
       </c>
       <c r="U16" s="20">
-        <v>373778</v>
+        <v>373779</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="7"/>
-        <v>0.92595400180346221</v>
+        <v>0.92595647908677425</v>
       </c>
       <c r="W16" s="16">
         <v>406853</v>
@@ -2714,14 +2714,14 @@
       </c>
       <c r="Y16" s="10">
         <f t="shared" si="8"/>
-        <v>87584</v>
+        <v>87585</v>
       </c>
       <c r="Z16" s="20">
-        <v>381196</v>
+        <v>381197</v>
       </c>
       <c r="AA16" s="12">
         <f t="shared" si="9"/>
-        <v>0.93693791123575343</v>
+        <v>0.93694036912594969</v>
       </c>
       <c r="AB16" s="17">
         <v>722282</v>
@@ -2731,14 +2731,14 @@
       </c>
       <c r="AD16" s="10">
         <f t="shared" si="10"/>
-        <v>123992</v>
+        <v>123995</v>
       </c>
       <c r="AE16" s="11">
-        <v>693621</v>
+        <v>693624</v>
       </c>
       <c r="AF16" s="12">
         <f t="shared" si="11"/>
-        <v>0.96031882284204784</v>
+        <v>0.96032297634441954</v>
       </c>
       <c r="AG16" s="16">
         <v>397671</v>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="AI16" s="10">
         <f t="shared" si="12"/>
-        <v>76333</v>
+        <v>76334</v>
       </c>
       <c r="AJ16" s="20">
-        <v>378735</v>
+        <v>378736</v>
       </c>
       <c r="AK16" s="12">
         <f t="shared" si="13"/>
-        <v>0.95238274855345251</v>
+        <v>0.95238526319495265</v>
       </c>
       <c r="AL16" s="18">
         <v>400740</v>
@@ -2765,14 +2765,14 @@
       </c>
       <c r="AN16" s="10">
         <f t="shared" si="14"/>
-        <v>77332</v>
+        <v>77333</v>
       </c>
       <c r="AO16" s="11">
-        <v>383657</v>
+        <v>383658</v>
       </c>
       <c r="AP16" s="12">
         <f t="shared" si="15"/>
-        <v>0.95737136297848979</v>
+        <v>0.95737385836203026</v>
       </c>
       <c r="AQ16" s="11">
         <v>730568</v>
@@ -2782,14 +2782,14 @@
       </c>
       <c r="AS16" s="10">
         <f t="shared" si="16"/>
-        <v>116470</v>
+        <v>116474</v>
       </c>
       <c r="AT16" s="13">
-        <v>703046</v>
+        <v>703050</v>
       </c>
       <c r="AU16" s="12">
         <f t="shared" si="17"/>
-        <v>0.96232794209437045</v>
+        <v>0.96233341728627586</v>
       </c>
       <c r="AV16" s="18">
         <v>402711</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="AX16" s="10">
         <f t="shared" si="18"/>
-        <v>74839</v>
+        <v>74840</v>
       </c>
       <c r="AY16" s="20">
-        <v>382482</v>
+        <v>382483</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="19"/>
-        <v>0.94976794773423123</v>
+        <v>0.94977043090454449</v>
       </c>
       <c r="BA16" s="18">
         <v>402569</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="BC16" s="10">
         <f t="shared" si="20"/>
-        <v>468325</v>
+        <v>80940</v>
       </c>
       <c r="BD16" s="20">
-        <v>774773</v>
+        <v>387388</v>
       </c>
       <c r="BE16" s="12">
         <f t="shared" si="21"/>
-        <v>1.924571936736311</v>
+        <v>0.96228969443747536</v>
       </c>
       <c r="BF16" s="18">
         <v>736680</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="BH16" s="10">
         <f t="shared" si="22"/>
-        <v>137191</v>
+        <v>137194</v>
       </c>
       <c r="BI16" s="11">
-        <v>709537</v>
+        <v>709540</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="23"/>
-        <v>0.96315496552098601</v>
+        <v>0.96315903784546886</v>
       </c>
       <c r="BK16" s="24"/>
       <c r="BL16" s="24"/>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" si="0"/>
-        <v>221393</v>
+        <v>221394</v>
       </c>
       <c r="F17" s="20">
-        <v>259931</v>
+        <v>259932</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="1"/>
-        <v>0.98487437623852414</v>
+        <v>0.98487816522243232</v>
       </c>
       <c r="H17" s="15">
         <v>264168</v>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="T17" s="10">
         <f t="shared" si="6"/>
-        <v>69622</v>
+        <v>69623</v>
       </c>
       <c r="U17" s="20">
-        <v>257380</v>
+        <v>257381</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="7"/>
-        <v>0.98532615145494296</v>
+        <v>0.98532997974832803</v>
       </c>
       <c r="W17" s="16">
         <v>269820</v>
@@ -2945,14 +2945,14 @@
       </c>
       <c r="AD17" s="10">
         <f t="shared" si="10"/>
-        <v>123891</v>
+        <v>123892</v>
       </c>
       <c r="AE17" s="11">
-        <v>604351</v>
+        <v>604352</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="11"/>
-        <v>0.98498284615321929</v>
+        <v>0.98498447597239092</v>
       </c>
       <c r="AG17" s="16">
         <v>263808</v>
@@ -2962,14 +2962,14 @@
       </c>
       <c r="AI17" s="10">
         <f t="shared" si="12"/>
-        <v>62440</v>
+        <v>62441</v>
       </c>
       <c r="AJ17" s="20">
-        <v>259626</v>
+        <v>259627</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="13"/>
-        <v>0.9841475618631732</v>
+        <v>0.98415135249878705</v>
       </c>
       <c r="AL17" s="18">
         <v>270212</v>
@@ -2979,14 +2979,14 @@
       </c>
       <c r="AN17" s="10">
         <f t="shared" si="14"/>
-        <v>62613</v>
+        <v>62614</v>
       </c>
       <c r="AO17" s="11">
-        <v>266625</v>
+        <v>266626</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="15"/>
-        <v>0.9867252379613044</v>
+        <v>0.98672893875919643</v>
       </c>
       <c r="AQ17" s="11">
         <v>633137</v>
@@ -2996,14 +2996,14 @@
       </c>
       <c r="AS17" s="10">
         <f t="shared" si="16"/>
-        <v>124229</v>
+        <v>124230</v>
       </c>
       <c r="AT17" s="13">
-        <v>619718</v>
+        <v>619719</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.97880553497900136</v>
+        <v>0.97880711441599533</v>
       </c>
       <c r="AV17" s="18">
         <v>270996</v>
@@ -3013,14 +3013,14 @@
       </c>
       <c r="AX17" s="10">
         <f t="shared" si="18"/>
-        <v>61989</v>
+        <v>61991</v>
       </c>
       <c r="AY17" s="20">
-        <v>265739</v>
+        <v>265741</v>
       </c>
       <c r="AZ17" s="12">
         <f t="shared" si="19"/>
-        <v>0.98060118968545662</v>
+        <v>0.98060856986818989</v>
       </c>
       <c r="BA17" s="18">
         <v>277009</v>
@@ -3030,14 +3030,14 @@
       </c>
       <c r="BC17" s="10">
         <f t="shared" si="20"/>
-        <v>340151</v>
+        <v>65563</v>
       </c>
       <c r="BD17" s="20">
-        <v>549181</v>
+        <v>274593</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="21"/>
-        <v>1.9825384734792011</v>
+        <v>0.9912782617171283</v>
       </c>
       <c r="BF17" s="18">
         <v>651560</v>
@@ -3047,14 +3047,14 @@
       </c>
       <c r="BH17" s="10">
         <f t="shared" si="22"/>
-        <v>160492</v>
+        <v>160494</v>
       </c>
       <c r="BI17" s="11">
-        <v>635897</v>
+        <v>635899</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.9759607710725029</v>
+        <v>0.97596384062864505</v>
       </c>
       <c r="BK17" s="24"/>
       <c r="BL17" s="24"/>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" si="0"/>
-        <v>625833</v>
+        <v>625834</v>
       </c>
       <c r="F18" s="20">
-        <v>740858</v>
+        <v>740859</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="1"/>
-        <v>0.96403875632080405</v>
+        <v>0.96404005756713784</v>
       </c>
       <c r="H18" s="15">
         <v>766983</v>
@@ -3091,14 +3091,14 @@
       </c>
       <c r="J18" s="10">
         <f t="shared" si="2"/>
-        <v>565000</v>
+        <v>565001</v>
       </c>
       <c r="K18" s="20">
-        <v>740262</v>
+        <v>740263</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="3"/>
-        <v>0.96516089665611882</v>
+        <v>0.96516220046598167</v>
       </c>
       <c r="M18" s="16">
         <v>1193073</v>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="O18" s="10">
         <f t="shared" si="4"/>
-        <v>410737</v>
+        <v>410738</v>
       </c>
       <c r="P18" s="13">
-        <v>1175487</v>
+        <v>1175488</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.98525991284690884</v>
+        <v>0.98526075101858812</v>
       </c>
       <c r="R18" s="16">
         <v>775495</v>
@@ -3125,14 +3125,14 @@
       </c>
       <c r="T18" s="10">
         <f t="shared" si="6"/>
-        <v>184176</v>
+        <v>184177</v>
       </c>
       <c r="U18" s="20">
-        <v>756205</v>
+        <v>756206</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="7"/>
-        <v>0.97512556496173408</v>
+        <v>0.97512685446069924</v>
       </c>
       <c r="W18" s="16">
         <v>789854</v>
@@ -3142,14 +3142,14 @@
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="8"/>
-        <v>178826</v>
+        <v>178827</v>
       </c>
       <c r="Z18" s="20">
-        <v>773187</v>
+        <v>773188</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="9"/>
-        <v>0.97889863189905979</v>
+        <v>0.97889989795582477</v>
       </c>
       <c r="AB18" s="17">
         <v>1245422</v>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="AD18" s="10">
         <f t="shared" si="10"/>
-        <v>240983</v>
+        <v>240984</v>
       </c>
       <c r="AE18" s="11">
-        <v>1213773</v>
+        <v>1213774</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.97458773010272826</v>
+        <v>0.97458853304341819</v>
       </c>
       <c r="AG18" s="16">
         <v>794310</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AI18" s="10">
         <f t="shared" si="12"/>
-        <v>158883</v>
+        <v>158884</v>
       </c>
       <c r="AJ18" s="20">
-        <v>773921</v>
+        <v>773922</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="13"/>
-        <v>0.97433118052145884</v>
+        <v>0.97433243947577142</v>
       </c>
       <c r="AL18" s="18">
         <v>807429</v>
@@ -3193,14 +3193,14 @@
       </c>
       <c r="AN18" s="10">
         <f t="shared" si="14"/>
-        <v>156233</v>
+        <v>156234</v>
       </c>
       <c r="AO18" s="11">
-        <v>787044</v>
+        <v>787045</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="15"/>
-        <v>0.97475319811401373</v>
+        <v>0.97475443661300254</v>
       </c>
       <c r="AQ18" s="11">
         <v>1285494</v>
@@ -3210,14 +3210,14 @@
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="16"/>
-        <v>230876</v>
+        <v>230878</v>
       </c>
       <c r="AT18" s="13">
-        <v>1245496</v>
+        <v>1245498</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.96888511342721162</v>
+        <v>0.96888666924933142</v>
       </c>
       <c r="AV18" s="18">
         <v>820095</v>
@@ -3244,14 +3244,14 @@
       </c>
       <c r="BC18" s="10">
         <f t="shared" si="20"/>
-        <v>1004683</v>
+        <v>198194</v>
       </c>
       <c r="BD18" s="20">
-        <v>1612984</v>
+        <v>806495</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="21"/>
-        <v>1.9434291442561642</v>
+        <v>0.97171818672527133</v>
       </c>
       <c r="BF18" s="18">
         <v>1319511</v>
@@ -3261,14 +3261,14 @@
       </c>
       <c r="BH18" s="10">
         <f t="shared" si="22"/>
-        <v>292043</v>
+        <v>292044</v>
       </c>
       <c r="BI18" s="11">
-        <v>1272821</v>
+        <v>1272822</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.96461567959645655</v>
+        <v>0.96461643745296555</v>
       </c>
       <c r="BK18" s="24"/>
       <c r="BL18" s="24"/>
@@ -3288,14 +3288,14 @@
       </c>
       <c r="E19" s="10">
         <f t="shared" si="0"/>
-        <v>181880</v>
+        <v>181881</v>
       </c>
       <c r="F19" s="20">
-        <v>215774</v>
+        <v>215775</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" si="1"/>
-        <v>0.87908121277306539</v>
+        <v>0.87908528685619303</v>
       </c>
       <c r="H19" s="15">
         <v>247965</v>
@@ -3305,14 +3305,14 @@
       </c>
       <c r="J19" s="10">
         <f t="shared" si="2"/>
-        <v>170660</v>
+        <v>170661</v>
       </c>
       <c r="K19" s="20">
-        <v>216750</v>
+        <v>216751</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="3"/>
-        <v>0.87411529853003445</v>
+        <v>0.87411933135724795</v>
       </c>
       <c r="M19" s="16">
         <v>387570</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="O19" s="10">
         <f t="shared" si="4"/>
-        <v>139739</v>
+        <v>139740</v>
       </c>
       <c r="P19" s="13">
-        <v>357137</v>
+        <v>357138</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="5"/>
-        <v>0.92147741053229093</v>
+        <v>0.92147999071135533</v>
       </c>
       <c r="R19" s="16">
         <v>254467</v>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="T19" s="10">
         <f t="shared" si="6"/>
-        <v>69080</v>
+        <v>69081</v>
       </c>
       <c r="U19" s="20">
-        <v>229791</v>
+        <v>229792</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="7"/>
-        <v>0.9030286834835165</v>
+        <v>0.90303261326616024</v>
       </c>
       <c r="W19" s="16">
         <v>263449</v>
@@ -3356,14 +3356,14 @@
       </c>
       <c r="Y19" s="10">
         <f t="shared" si="8"/>
-        <v>66519</v>
+        <v>66520</v>
       </c>
       <c r="Z19" s="20">
-        <v>244528</v>
+        <v>244529</v>
       </c>
       <c r="AA19" s="12">
         <f t="shared" si="9"/>
-        <v>0.92817964767374328</v>
+        <v>0.92818344347482817</v>
       </c>
       <c r="AB19" s="17">
         <v>418128</v>
@@ -3373,14 +3373,14 @@
       </c>
       <c r="AD19" s="10">
         <f t="shared" si="10"/>
-        <v>85784</v>
+        <v>85785</v>
       </c>
       <c r="AE19" s="11">
-        <v>394358</v>
+        <v>394359</v>
       </c>
       <c r="AF19" s="12">
         <f t="shared" si="11"/>
-        <v>0.9431513794818811</v>
+        <v>0.9431537710940191</v>
       </c>
       <c r="AG19" s="16">
         <v>259213</v>
@@ -3390,14 +3390,14 @@
       </c>
       <c r="AI19" s="10">
         <f t="shared" si="12"/>
-        <v>59058</v>
+        <v>59059</v>
       </c>
       <c r="AJ19" s="20">
-        <v>234182</v>
+        <v>234183</v>
       </c>
       <c r="AK19" s="12">
         <f t="shared" si="13"/>
-        <v>0.90343462712132494</v>
+        <v>0.90343848495252943</v>
       </c>
       <c r="AL19" s="18">
         <v>262802</v>
@@ -3407,14 +3407,14 @@
       </c>
       <c r="AN19" s="10">
         <f t="shared" si="14"/>
-        <v>55774</v>
+        <v>55775</v>
       </c>
       <c r="AO19" s="11">
-        <v>237109</v>
+        <v>237110</v>
       </c>
       <c r="AP19" s="12">
         <f t="shared" si="15"/>
-        <v>0.90223438177791648</v>
+        <v>0.90223818692399604</v>
       </c>
       <c r="AQ19" s="11">
         <v>437396</v>
@@ -3424,14 +3424,14 @@
       </c>
       <c r="AS19" s="10">
         <f t="shared" si="16"/>
-        <v>82226</v>
+        <v>82227</v>
       </c>
       <c r="AT19" s="13">
-        <v>401089</v>
+        <v>401090</v>
       </c>
       <c r="AU19" s="12">
         <f t="shared" si="17"/>
-        <v>0.91699283944068988</v>
+        <v>0.91699512569845176</v>
       </c>
       <c r="AV19" s="18">
         <v>265429</v>
@@ -3441,14 +3441,14 @@
       </c>
       <c r="AX19" s="10">
         <f t="shared" si="18"/>
-        <v>56299</v>
+        <v>56300</v>
       </c>
       <c r="AY19" s="20">
-        <v>237906</v>
+        <v>237907</v>
       </c>
       <c r="AZ19" s="12">
         <f t="shared" si="19"/>
-        <v>0.89630748712461716</v>
+        <v>0.89631125461046079</v>
       </c>
       <c r="BA19" s="18">
         <v>272122</v>
@@ -3458,14 +3458,14 @@
       </c>
       <c r="BC19" s="10">
         <f t="shared" si="20"/>
-        <v>310776</v>
+        <v>65961</v>
       </c>
       <c r="BD19" s="20">
-        <v>489634</v>
+        <v>244819</v>
       </c>
       <c r="BE19" s="12">
         <f t="shared" si="21"/>
-        <v>1.7993179529769736</v>
+        <v>0.89966632613313147</v>
       </c>
       <c r="BF19" s="18">
         <v>456786</v>
@@ -3475,14 +3475,14 @@
       </c>
       <c r="BH19" s="10">
         <f t="shared" si="22"/>
-        <v>115391</v>
+        <v>115393</v>
       </c>
       <c r="BI19" s="11">
-        <v>415713</v>
+        <v>415715</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="23"/>
-        <v>0.91008262074581969</v>
+        <v>0.91008699916372215</v>
       </c>
       <c r="BK19" s="24"/>
       <c r="BL19" s="24"/>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="BC20" s="10">
         <f t="shared" si="20"/>
-        <v>6617</v>
+        <v>1555</v>
       </c>
       <c r="BD20" s="20">
-        <v>10125</v>
+        <v>5063</v>
       </c>
       <c r="BE20" s="12">
         <f t="shared" si="21"/>
-        <v>1.7126184032476319</v>
+        <v>0.85639377537212447</v>
       </c>
       <c r="BF20" s="18">
         <v>8941</v>
@@ -3767,14 +3767,14 @@
       </c>
       <c r="T21" s="10">
         <f t="shared" si="6"/>
-        <v>3584</v>
+        <v>3585</v>
       </c>
       <c r="U21" s="20">
-        <v>7870</v>
+        <v>7871</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="7"/>
-        <v>0.76877991599101303</v>
+        <v>0.76887760085962686</v>
       </c>
       <c r="W21" s="16">
         <v>10162</v>
@@ -3784,14 +3784,14 @@
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="8"/>
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="Z21" s="20">
-        <v>7972</v>
+        <v>7973</v>
       </c>
       <c r="AA21" s="12">
         <f t="shared" si="9"/>
-        <v>0.78449124188151942</v>
+        <v>0.78458964770714423</v>
       </c>
       <c r="AB21" s="17">
         <v>13196</v>
@@ -3801,14 +3801,14 @@
       </c>
       <c r="AD21" s="10">
         <f t="shared" si="10"/>
-        <v>4246</v>
+        <v>4247</v>
       </c>
       <c r="AE21" s="11">
-        <v>10798</v>
+        <v>10799</v>
       </c>
       <c r="AF21" s="12">
         <f t="shared" si="11"/>
-        <v>0.81827826614125487</v>
+        <v>0.81835404668081235</v>
       </c>
       <c r="AG21" s="16">
         <v>10295</v>
@@ -3818,14 +3818,14 @@
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="12"/>
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="AJ21" s="20">
-        <v>8033</v>
+        <v>8034</v>
       </c>
       <c r="AK21" s="12">
         <f t="shared" si="13"/>
-        <v>0.78028169014084503</v>
+        <v>0.78037882467217101</v>
       </c>
       <c r="AL21" s="18">
         <v>10459</v>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="14"/>
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="AO21" s="11">
-        <v>8141</v>
+        <v>8142</v>
       </c>
       <c r="AP21" s="12">
         <f t="shared" si="15"/>
-        <v>0.77837269337412751</v>
+        <v>0.77846830480925522</v>
       </c>
       <c r="AQ21" s="11">
         <v>13595</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="AS21" s="10">
         <f t="shared" si="16"/>
-        <v>3829</v>
+        <v>3830</v>
       </c>
       <c r="AT21" s="13">
-        <v>11062</v>
+        <v>11063</v>
       </c>
       <c r="AU21" s="12">
         <f t="shared" si="17"/>
-        <v>0.81368150055167343</v>
+        <v>0.81375505700625228</v>
       </c>
       <c r="AV21" s="18">
         <v>10391</v>
@@ -3869,14 +3869,14 @@
       </c>
       <c r="AX21" s="10">
         <f t="shared" si="18"/>
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="AY21" s="20">
-        <v>8240</v>
+        <v>8241</v>
       </c>
       <c r="AZ21" s="12">
         <f t="shared" si="19"/>
-        <v>0.79299393706091814</v>
+        <v>0.79309017418920225</v>
       </c>
       <c r="BA21" s="18">
         <v>10525</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="BC21" s="10">
         <f t="shared" si="20"/>
-        <v>11508</v>
+        <v>3121</v>
       </c>
       <c r="BD21" s="20">
-        <v>16777</v>
+        <v>8390</v>
       </c>
       <c r="BE21" s="12">
         <f t="shared" si="21"/>
-        <v>1.5940142517814726</v>
+        <v>0.79714964370546315</v>
       </c>
       <c r="BF21" s="18">
         <v>13618</v>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="BH21" s="10">
         <f t="shared" si="22"/>
-        <v>5149</v>
+        <v>5150</v>
       </c>
       <c r="BI21" s="11">
-        <v>11449</v>
+        <v>11450</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="23"/>
-        <v>0.84072551035394327</v>
+        <v>0.8407989425760023</v>
       </c>
       <c r="BK21" s="24"/>
       <c r="BL21" s="24"/>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="BC22" s="10">
         <f t="shared" si="20"/>
-        <v>7086</v>
+        <v>1610</v>
       </c>
       <c r="BD22" s="20">
-        <v>10952</v>
+        <v>5476</v>
       </c>
       <c r="BE22" s="12">
         <f t="shared" si="21"/>
-        <v>1.8262464565616141</v>
+        <v>0.91312322828080705</v>
       </c>
       <c r="BF22" s="18">
         <v>7214</v>
@@ -4144,14 +4144,14 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" si="0"/>
-        <v>6140</v>
+        <v>6141</v>
       </c>
       <c r="F23" s="20">
-        <v>7287</v>
+        <v>7288</v>
       </c>
       <c r="G23" s="12">
         <f t="shared" si="1"/>
-        <v>0.76867088607594936</v>
+        <v>0.7687763713080169</v>
       </c>
       <c r="H23" s="15">
         <v>9486</v>
@@ -4161,14 +4161,14 @@
       </c>
       <c r="J23" s="10">
         <f t="shared" si="2"/>
-        <v>5885</v>
+        <v>5886</v>
       </c>
       <c r="K23" s="20">
-        <v>7258</v>
+        <v>7259</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="3"/>
-        <v>0.76512755639890362</v>
+        <v>0.76523297491039421</v>
       </c>
       <c r="M23" s="16">
         <v>11077</v>
@@ -4178,14 +4178,14 @@
       </c>
       <c r="O23" s="10">
         <f t="shared" si="4"/>
-        <v>5405</v>
+        <v>5406</v>
       </c>
       <c r="P23" s="13">
-        <v>8722</v>
+        <v>8723</v>
       </c>
       <c r="Q23" s="12">
         <f t="shared" si="5"/>
-        <v>0.78739730974090461</v>
+        <v>0.78748758689175768</v>
       </c>
       <c r="R23" s="16">
         <v>9575</v>
@@ -4314,14 +4314,14 @@
       </c>
       <c r="BC23" s="10">
         <f t="shared" si="20"/>
-        <v>10873</v>
+        <v>3263</v>
       </c>
       <c r="BD23" s="20">
-        <v>15221</v>
+        <v>7611</v>
       </c>
       <c r="BE23" s="12">
         <f t="shared" si="21"/>
-        <v>1.7162025031006878</v>
+        <v>0.8581576276919608</v>
       </c>
       <c r="BF23" s="18">
         <v>10711</v>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="BC24" s="10">
         <f t="shared" si="20"/>
-        <v>6338</v>
+        <v>1304</v>
       </c>
       <c r="BD24" s="20">
-        <v>10070</v>
+        <v>5036</v>
       </c>
       <c r="BE24" s="12">
         <f t="shared" si="21"/>
-        <v>1.6397980784888455</v>
+        <v>0.82006187917277318</v>
       </c>
       <c r="BF24" s="18">
         <v>7097</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="E25" s="10">
         <f t="shared" si="0"/>
-        <v>12801</v>
+        <v>12802</v>
       </c>
       <c r="F25" s="20">
-        <v>16173</v>
+        <v>16174</v>
       </c>
       <c r="G25" s="12">
         <f t="shared" si="1"/>
-        <v>0.89353591160220991</v>
+        <v>0.8935911602209945</v>
       </c>
       <c r="H25" s="15">
         <v>17996</v>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="J25" s="10">
         <f t="shared" si="2"/>
-        <v>13568</v>
+        <v>13569</v>
       </c>
       <c r="K25" s="20">
-        <v>16245</v>
+        <v>16246</v>
       </c>
       <c r="L25" s="12">
         <f t="shared" si="3"/>
-        <v>0.90270060013336295</v>
+        <v>0.9027561680373416</v>
       </c>
       <c r="M25" s="16">
         <v>25145</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="O25" s="10">
         <f t="shared" si="4"/>
-        <v>9471</v>
+        <v>9472</v>
       </c>
       <c r="P25" s="13">
-        <v>23171</v>
+        <v>23172</v>
       </c>
       <c r="Q25" s="12">
         <f t="shared" si="5"/>
-        <v>0.92149532710280369</v>
+        <v>0.92153509644064424</v>
       </c>
       <c r="R25" s="16">
         <v>18343</v>
@@ -4623,14 +4623,14 @@
       </c>
       <c r="T25" s="10">
         <f t="shared" si="6"/>
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="U25" s="20">
-        <v>16457</v>
+        <v>16458</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="7"/>
-        <v>0.89718148612549742</v>
+        <v>0.89723600283486893</v>
       </c>
       <c r="W25" s="16">
         <v>18513</v>
@@ -4640,14 +4640,14 @@
       </c>
       <c r="Y25" s="10">
         <f t="shared" si="8"/>
-        <v>4127</v>
+        <v>4128</v>
       </c>
       <c r="Z25" s="20">
-        <v>16651</v>
+        <v>16652</v>
       </c>
       <c r="AA25" s="12">
         <f t="shared" si="9"/>
-        <v>0.89942202776427371</v>
+        <v>0.89947604386107061</v>
       </c>
       <c r="AB25" s="17">
         <v>25418</v>
@@ -4657,14 +4657,14 @@
       </c>
       <c r="AD25" s="10">
         <f t="shared" si="10"/>
-        <v>5449</v>
+        <v>5450</v>
       </c>
       <c r="AE25" s="11">
-        <v>23608</v>
+        <v>23609</v>
       </c>
       <c r="AF25" s="12">
         <f t="shared" si="11"/>
-        <v>0.92879062081989139</v>
+        <v>0.92882996301833343</v>
       </c>
       <c r="AG25" s="16">
         <v>18377</v>
@@ -4674,14 +4674,14 @@
       </c>
       <c r="AI25" s="10">
         <f t="shared" si="12"/>
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="AJ25" s="20">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="AK25" s="12">
         <f t="shared" si="13"/>
-        <v>0.90667682429123364</v>
+        <v>0.90673124013712791</v>
       </c>
       <c r="AL25" s="18">
         <v>18561</v>
@@ -4691,14 +4691,14 @@
       </c>
       <c r="AN25" s="10">
         <f t="shared" si="14"/>
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="AO25" s="11">
-        <v>16817</v>
+        <v>16818</v>
       </c>
       <c r="AP25" s="12">
         <f t="shared" si="15"/>
-        <v>0.90603954528312047</v>
+        <v>0.90609342169064166</v>
       </c>
       <c r="AQ25" s="11">
         <v>25768</v>
@@ -4708,14 +4708,14 @@
       </c>
       <c r="AS25" s="10">
         <f t="shared" si="16"/>
-        <v>4297</v>
+        <v>4298</v>
       </c>
       <c r="AT25" s="13">
-        <v>23886</v>
+        <v>23887</v>
       </c>
       <c r="AU25" s="12">
         <f t="shared" si="17"/>
-        <v>0.92696367587705686</v>
+        <v>0.92700248370071403</v>
       </c>
       <c r="AV25" s="18">
         <v>18472</v>
@@ -4725,14 +4725,14 @@
       </c>
       <c r="AX25" s="10">
         <f t="shared" si="18"/>
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="AY25" s="20">
-        <v>17022</v>
+        <v>17023</v>
       </c>
       <c r="AZ25" s="12">
         <f t="shared" si="19"/>
-        <v>0.92150281507145948</v>
+        <v>0.92155695106106539</v>
       </c>
       <c r="BA25" s="18">
         <v>18607</v>
@@ -4742,14 +4742,14 @@
       </c>
       <c r="BC25" s="10">
         <f t="shared" si="20"/>
-        <v>20871</v>
+        <v>3559</v>
       </c>
       <c r="BD25" s="20">
-        <v>34626</v>
+        <v>17314</v>
       </c>
       <c r="BE25" s="12">
         <f t="shared" si="21"/>
-        <v>1.8609125597893266</v>
+        <v>0.93051002310958242</v>
       </c>
       <c r="BF25" s="18">
         <v>26131</v>
@@ -4759,14 +4759,14 @@
       </c>
       <c r="BH25" s="10">
         <f t="shared" si="22"/>
-        <v>6379</v>
+        <v>6380</v>
       </c>
       <c r="BI25" s="11">
-        <v>24500</v>
+        <v>24501</v>
       </c>
       <c r="BJ25" s="12">
         <f t="shared" si="23"/>
-        <v>0.93758371283150277</v>
+        <v>0.93762198155447551</v>
       </c>
       <c r="BK25" s="24"/>
       <c r="BL25" s="24"/>
@@ -4786,14 +4786,14 @@
       </c>
       <c r="E26" s="10">
         <f t="shared" si="0"/>
-        <v>9673</v>
+        <v>9675</v>
       </c>
       <c r="F26" s="20">
-        <v>13149</v>
+        <v>13151</v>
       </c>
       <c r="G26" s="12">
         <f t="shared" si="1"/>
-        <v>0.79392585436541485</v>
+        <v>0.79404661272793142</v>
       </c>
       <c r="H26" s="15">
         <v>16580</v>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="J26" s="10">
         <f t="shared" si="2"/>
-        <v>9477</v>
+        <v>9478</v>
       </c>
       <c r="K26" s="20">
-        <v>13082</v>
+        <v>13083</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="3"/>
-        <v>0.78902291917973466</v>
+        <v>0.78908323281061521</v>
       </c>
       <c r="M26" s="16">
         <v>25396</v>
@@ -4820,14 +4820,14 @@
       </c>
       <c r="O26" s="10">
         <f t="shared" si="4"/>
-        <v>8462</v>
+        <v>8464</v>
       </c>
       <c r="P26" s="13">
-        <v>21705</v>
+        <v>21707</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="5"/>
-        <v>0.85466215151992442</v>
+        <v>0.85474090407938264</v>
       </c>
       <c r="R26" s="16">
         <v>16475</v>
@@ -4837,14 +4837,14 @@
       </c>
       <c r="T26" s="10">
         <f t="shared" si="6"/>
-        <v>4395</v>
+        <v>4396</v>
       </c>
       <c r="U26" s="20">
-        <v>12978</v>
+        <v>12979</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="7"/>
-        <v>0.78773899848254936</v>
+        <v>0.78779969650986348</v>
       </c>
       <c r="W26" s="16">
         <v>16675</v>
@@ -4854,14 +4854,14 @@
       </c>
       <c r="Y26" s="10">
         <f t="shared" si="8"/>
-        <v>3964</v>
+        <v>3965</v>
       </c>
       <c r="Z26" s="20">
-        <v>13243</v>
+        <v>13244</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="9"/>
-        <v>0.79418290854572715</v>
+        <v>0.79424287856071962</v>
       </c>
       <c r="AB26" s="17">
         <v>25656</v>
@@ -4871,14 +4871,14 @@
       </c>
       <c r="AD26" s="10">
         <f t="shared" si="10"/>
-        <v>5326</v>
+        <v>5329</v>
       </c>
       <c r="AE26" s="11">
-        <v>22437</v>
+        <v>22440</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="11"/>
-        <v>0.87453227315247895</v>
+        <v>0.87464920486435926</v>
       </c>
       <c r="AG26" s="16">
         <v>15844</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="AI26" s="10">
         <f t="shared" si="12"/>
-        <v>3554</v>
+        <v>3555</v>
       </c>
       <c r="AJ26" s="20">
-        <v>12771</v>
+        <v>12772</v>
       </c>
       <c r="AK26" s="12">
         <f t="shared" si="13"/>
-        <v>0.80604645291593036</v>
+        <v>0.80610956829083569</v>
       </c>
       <c r="AL26" s="18">
         <v>16081</v>
@@ -4905,14 +4905,14 @@
       </c>
       <c r="AN26" s="10">
         <f t="shared" si="14"/>
-        <v>3492</v>
+        <v>3495</v>
       </c>
       <c r="AO26" s="11">
-        <v>12978</v>
+        <v>12981</v>
       </c>
       <c r="AP26" s="12">
         <f t="shared" si="15"/>
-        <v>0.80703936322368008</v>
+        <v>0.80722591878614514</v>
       </c>
       <c r="AQ26" s="11">
         <v>26317</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="AS26" s="10">
         <f t="shared" si="16"/>
-        <v>5521</v>
+        <v>5525</v>
       </c>
       <c r="AT26" s="13">
-        <v>22881</v>
+        <v>22885</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="17"/>
-        <v>0.86943800585173081</v>
+        <v>0.86958999886005239</v>
       </c>
       <c r="AV26" s="18">
         <v>15987</v>
@@ -4939,14 +4939,14 @@
       </c>
       <c r="AX26" s="10">
         <f t="shared" si="18"/>
-        <v>3714</v>
+        <v>3716</v>
       </c>
       <c r="AY26" s="20">
-        <v>12837</v>
+        <v>12839</v>
       </c>
       <c r="AZ26" s="12">
         <f t="shared" si="19"/>
-        <v>0.80296490898855322</v>
+        <v>0.80309001063363983</v>
       </c>
       <c r="BA26" s="18">
         <v>16133</v>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="BC26" s="10">
         <f t="shared" si="20"/>
-        <v>16810</v>
+        <v>3787</v>
       </c>
       <c r="BD26" s="20">
-        <v>26050</v>
+        <v>13027</v>
       </c>
       <c r="BE26" s="12">
         <f t="shared" si="21"/>
-        <v>1.6147027831153535</v>
+        <v>0.8074753610611789</v>
       </c>
       <c r="BF26" s="18">
         <v>26642</v>
@@ -4973,14 +4973,14 @@
       </c>
       <c r="BH26" s="10">
         <f t="shared" si="22"/>
-        <v>6319</v>
+        <v>6323</v>
       </c>
       <c r="BI26" s="11">
-        <v>23225</v>
+        <v>23229</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="23"/>
-        <v>0.87174386307334284</v>
+        <v>0.87189400195180544</v>
       </c>
       <c r="BK26" s="24"/>
       <c r="BL26" s="24"/>
@@ -5000,14 +5000,14 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" si="0"/>
-        <v>84777</v>
+        <v>84778</v>
       </c>
       <c r="F27" s="20">
-        <v>102181</v>
+        <v>102182</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="1"/>
-        <v>0.90556289160470416</v>
+        <v>0.90557175394595746</v>
       </c>
       <c r="H27" s="15">
         <v>111842</v>
@@ -5017,14 +5017,14 @@
       </c>
       <c r="J27" s="10">
         <f t="shared" si="2"/>
-        <v>84483</v>
+        <v>84484</v>
       </c>
       <c r="K27" s="20">
-        <v>102035</v>
+        <v>102036</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="3"/>
-        <v>0.9123137998247528</v>
+        <v>0.91232274100963862</v>
       </c>
       <c r="M27" s="16">
         <v>156288</v>
@@ -5034,14 +5034,14 @@
       </c>
       <c r="O27" s="10">
         <f t="shared" si="4"/>
-        <v>74506</v>
+        <v>74508</v>
       </c>
       <c r="P27" s="13">
-        <v>145759</v>
+        <v>145761</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="5"/>
-        <v>0.93263078419328416</v>
+        <v>0.93264358108108103</v>
       </c>
       <c r="R27" s="16">
         <v>113087</v>
@@ -5051,14 +5051,14 @@
       </c>
       <c r="T27" s="10">
         <f t="shared" si="6"/>
-        <v>39379</v>
+        <v>39381</v>
       </c>
       <c r="U27" s="20">
-        <v>104507</v>
+        <v>104509</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="7"/>
-        <v>0.92412921025405215</v>
+        <v>0.92414689575282749</v>
       </c>
       <c r="W27" s="16">
         <v>116164</v>
@@ -5068,14 +5068,14 @@
       </c>
       <c r="Y27" s="10">
         <f t="shared" si="8"/>
-        <v>38424</v>
+        <v>38428</v>
       </c>
       <c r="Z27" s="20">
-        <v>108034</v>
+        <v>108038</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="9"/>
-        <v>0.93001274060810579</v>
+        <v>0.93004717468406739</v>
       </c>
       <c r="AB27" s="17">
         <v>165468</v>
@@ -5085,14 +5085,14 @@
       </c>
       <c r="AD27" s="10">
         <f t="shared" si="10"/>
-        <v>48105</v>
+        <v>48109</v>
       </c>
       <c r="AE27" s="11">
-        <v>155644</v>
+        <v>155648</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="11"/>
-        <v>0.94062900379529579</v>
+        <v>0.94065317765368528</v>
       </c>
       <c r="AG27" s="16">
         <v>116084</v>
@@ -5102,14 +5102,14 @@
       </c>
       <c r="AI27" s="10">
         <f t="shared" si="12"/>
-        <v>32769</v>
+        <v>32774</v>
       </c>
       <c r="AJ27" s="20">
-        <v>107146</v>
+        <v>107151</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="13"/>
-        <v>0.92300403156335065</v>
+        <v>0.92304710382137078</v>
       </c>
       <c r="AL27" s="18">
         <v>117992</v>
@@ -5119,14 +5119,14 @@
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="14"/>
-        <v>33353</v>
+        <v>33358</v>
       </c>
       <c r="AO27" s="11">
-        <v>109177</v>
+        <v>109182</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="15"/>
-        <v>0.92529154518950441</v>
+        <v>0.92533392094379285</v>
       </c>
       <c r="AQ27" s="11">
         <v>170879</v>
@@ -5136,14 +5136,14 @@
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="16"/>
-        <v>45165</v>
+        <v>45170</v>
       </c>
       <c r="AT27" s="13">
-        <v>160515</v>
+        <v>160520</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="17"/>
-        <v>0.93934889600243443</v>
+        <v>0.93937815647329392</v>
       </c>
       <c r="AV27" s="18">
         <v>116485</v>
@@ -5153,14 +5153,14 @@
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="18"/>
-        <v>34165</v>
+        <v>34170</v>
       </c>
       <c r="AY27" s="20">
-        <v>109522</v>
+        <v>109527</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="19"/>
-        <v>0.94022406318410101</v>
+        <v>0.94026698716572954</v>
       </c>
       <c r="BA27" s="18">
         <v>117017</v>
@@ -5170,14 +5170,14 @@
       </c>
       <c r="BC27" s="10">
         <f t="shared" si="20"/>
-        <v>149525</v>
+        <v>38118</v>
       </c>
       <c r="BD27" s="20">
-        <v>222827</v>
+        <v>111420</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="21"/>
-        <v>1.9042275908628661</v>
+        <v>0.95216934291598654</v>
       </c>
       <c r="BF27" s="18">
         <v>172738</v>
@@ -5187,14 +5187,14 @@
       </c>
       <c r="BH27" s="10">
         <f t="shared" si="22"/>
-        <v>63112</v>
+        <v>63117</v>
       </c>
       <c r="BI27" s="11">
-        <v>164657</v>
+        <v>164662</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="23"/>
-        <v>0.95321816855584762</v>
+        <v>0.95324711412659635</v>
       </c>
       <c r="BK27" s="24"/>
       <c r="BL27" s="24"/>
@@ -5350,14 +5350,14 @@
       </c>
       <c r="AS28" s="10">
         <f t="shared" si="16"/>
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="AT28" s="13">
-        <v>590273</v>
+        <v>590274</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="17"/>
-        <v>0.95603464751594547</v>
+        <v>0.95603626716422263</v>
       </c>
       <c r="AV28" s="18">
         <v>357852</v>
@@ -5384,14 +5384,14 @@
       </c>
       <c r="BC28" s="10">
         <f t="shared" si="20"/>
-        <v>418089</v>
+        <v>73131</v>
       </c>
       <c r="BD28" s="20">
-        <v>689917</v>
+        <v>344959</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="21"/>
-        <v>1.9167395948803005</v>
+        <v>0.95837118654898135</v>
       </c>
       <c r="BF28" s="18">
         <v>622234</v>
@@ -5401,14 +5401,14 @@
       </c>
       <c r="BH28" s="10">
         <f t="shared" si="22"/>
-        <v>124735</v>
+        <v>124736</v>
       </c>
       <c r="BI28" s="11">
-        <v>600527</v>
+        <v>600528</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="23"/>
-        <v>0.96511441033437584</v>
+        <v>0.96511601744681264</v>
       </c>
       <c r="BK28" s="24"/>
       <c r="BL28" s="24"/>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="AD29" s="10">
         <f t="shared" si="10"/>
-        <v>33491</v>
+        <v>33492</v>
       </c>
       <c r="AE29" s="11">
-        <v>154121</v>
+        <v>154122</v>
       </c>
       <c r="AF29" s="12">
         <f t="shared" si="11"/>
-        <v>0.96231198136828233</v>
+        <v>0.96231822524148181</v>
       </c>
       <c r="AG29" s="16">
         <v>115309</v>
@@ -5530,14 +5530,14 @@
       </c>
       <c r="AI29" s="10">
         <f t="shared" si="12"/>
-        <v>25253</v>
+        <v>25254</v>
       </c>
       <c r="AJ29" s="20">
-        <v>109814</v>
+        <v>109815</v>
       </c>
       <c r="AK29" s="12">
         <f t="shared" si="13"/>
-        <v>0.95234543704307562</v>
+        <v>0.95235410939302223</v>
       </c>
       <c r="AL29" s="18">
         <v>116530</v>
@@ -5547,14 +5547,14 @@
       </c>
       <c r="AN29" s="10">
         <f t="shared" si="14"/>
-        <v>23999</v>
+        <v>24000</v>
       </c>
       <c r="AO29" s="11">
-        <v>110930</v>
+        <v>110931</v>
       </c>
       <c r="AP29" s="12">
         <f t="shared" si="15"/>
-        <v>0.95194370548356644</v>
+        <v>0.95195228696473011</v>
       </c>
       <c r="AQ29" s="11">
         <v>164389</v>
@@ -5564,14 +5564,14 @@
       </c>
       <c r="AS29" s="10">
         <f t="shared" si="16"/>
-        <v>29548</v>
+        <v>29550</v>
       </c>
       <c r="AT29" s="13">
-        <v>157112</v>
+        <v>157114</v>
       </c>
       <c r="AU29" s="12">
         <f t="shared" si="17"/>
-        <v>0.95573304783166757</v>
+        <v>0.95574521409583368</v>
       </c>
       <c r="AV29" s="18">
         <v>118862</v>
@@ -5581,14 +5581,14 @@
       </c>
       <c r="AX29" s="10">
         <f t="shared" si="18"/>
-        <v>23780</v>
+        <v>23781</v>
       </c>
       <c r="AY29" s="20">
-        <v>112720</v>
+        <v>112721</v>
       </c>
       <c r="AZ29" s="12">
         <f t="shared" si="19"/>
-        <v>0.94832663088287261</v>
+        <v>0.94833504400060575</v>
       </c>
       <c r="BA29" s="18">
         <v>119046</v>
@@ -5598,14 +5598,14 @@
       </c>
       <c r="BC29" s="10">
         <f t="shared" si="20"/>
-        <v>143890</v>
+        <v>29756</v>
       </c>
       <c r="BD29" s="20">
-        <v>228271</v>
+        <v>114137</v>
       </c>
       <c r="BE29" s="12">
         <f t="shared" si="21"/>
-        <v>1.9175024780337013</v>
+        <v>0.95876383918821295</v>
       </c>
       <c r="BF29" s="18">
         <v>167253</v>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="BH29" s="10">
         <f t="shared" si="22"/>
-        <v>41681</v>
+        <v>41683</v>
       </c>
       <c r="BI29" s="11">
-        <v>160685</v>
+        <v>160687</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="23"/>
-        <v>0.9607301513276294</v>
+        <v>0.96074210925962467</v>
       </c>
       <c r="BK29" s="24"/>
       <c r="BL29" s="24"/>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" si="0"/>
-        <v>116753</v>
+        <v>116754</v>
       </c>
       <c r="F30" s="20">
-        <v>143237</v>
+        <v>143238</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="1"/>
-        <v>0.95928126067360042</v>
+        <v>0.95928795783467391</v>
       </c>
       <c r="H30" s="15">
         <v>149659</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="BC30" s="10">
         <f t="shared" si="20"/>
-        <v>192661</v>
+        <v>41866</v>
       </c>
       <c r="BD30" s="20">
-        <v>301591</v>
+        <v>150796</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="21"/>
-        <v>1.9227375601670333</v>
+        <v>0.96137196774090716</v>
       </c>
       <c r="BF30" s="18">
         <v>270589</v>
@@ -5907,14 +5907,14 @@
       </c>
       <c r="T31" s="10">
         <f t="shared" si="6"/>
-        <v>26573</v>
+        <v>26574</v>
       </c>
       <c r="U31" s="20">
-        <v>69426</v>
+        <v>69427</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="7"/>
-        <v>0.95348358122862675</v>
+        <v>0.95349731503989676</v>
       </c>
       <c r="W31" s="16">
         <v>74776</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="Y31" s="10">
         <f t="shared" si="8"/>
-        <v>26361</v>
+        <v>26362</v>
       </c>
       <c r="Z31" s="20">
-        <v>71218</v>
+        <v>71219</v>
       </c>
       <c r="AA31" s="12">
         <f t="shared" si="9"/>
-        <v>0.9524178880924361</v>
+        <v>0.95243126136728362</v>
       </c>
       <c r="AB31" s="17">
         <v>124489</v>
@@ -5941,14 +5941,14 @@
       </c>
       <c r="AD31" s="10">
         <f t="shared" si="10"/>
-        <v>35715</v>
+        <v>35717</v>
       </c>
       <c r="AE31" s="11">
-        <v>119900</v>
+        <v>119902</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="11"/>
-        <v>0.96313730530408315</v>
+        <v>0.96315337098056852</v>
       </c>
       <c r="AG31" s="16">
         <v>73552</v>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="AI31" s="10">
         <f t="shared" si="12"/>
-        <v>22348</v>
+        <v>22349</v>
       </c>
       <c r="AJ31" s="20">
-        <v>69290</v>
+        <v>69291</v>
       </c>
       <c r="AK31" s="12">
         <f t="shared" si="13"/>
-        <v>0.94205460082662607</v>
+        <v>0.94206819664998909</v>
       </c>
       <c r="AL31" s="18">
         <v>74464</v>
@@ -5992,14 +5992,14 @@
       </c>
       <c r="AS31" s="10">
         <f t="shared" si="16"/>
-        <v>34483</v>
+        <v>34485</v>
       </c>
       <c r="AT31" s="13">
-        <v>122372</v>
+        <v>122374</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="17"/>
-        <v>0.96625238854760509</v>
+        <v>0.96626818059788699</v>
       </c>
       <c r="AV31" s="18">
         <v>72827</v>
@@ -6026,14 +6026,14 @@
       </c>
       <c r="BC31" s="10">
         <f t="shared" si="20"/>
-        <v>97273</v>
+        <v>25490</v>
       </c>
       <c r="BD31" s="20">
-        <v>143566</v>
+        <v>71783</v>
       </c>
       <c r="BE31" s="12">
         <f t="shared" si="21"/>
-        <v>1.9406580334694099</v>
+        <v>0.97032901673470495</v>
       </c>
       <c r="BF31" s="18">
         <v>129555</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BH31" s="10">
         <f t="shared" si="22"/>
-        <v>48862</v>
+        <v>48864</v>
       </c>
       <c r="BI31" s="11">
-        <v>125623</v>
+        <v>125625</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="23"/>
-        <v>0.96964995561730538</v>
+        <v>0.96966539307629962</v>
       </c>
       <c r="BK31" s="24"/>
       <c r="BL31" s="24"/>
@@ -6070,14 +6070,14 @@
       </c>
       <c r="E32" s="10">
         <f t="shared" si="0"/>
-        <v>153245</v>
+        <v>153246</v>
       </c>
       <c r="F32" s="20">
-        <v>183454</v>
+        <v>183455</v>
       </c>
       <c r="G32" s="12">
         <f t="shared" si="1"/>
-        <v>0.98811274311783304</v>
+        <v>0.98811812927863152</v>
       </c>
       <c r="H32" s="15">
         <v>186389</v>
@@ -6087,14 +6087,14 @@
       </c>
       <c r="J32" s="10">
         <f t="shared" si="2"/>
-        <v>138218</v>
+        <v>138219</v>
       </c>
       <c r="K32" s="20">
-        <v>183855</v>
+        <v>183856</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" si="3"/>
-        <v>0.9864047771059451</v>
+        <v>0.98641014222942336</v>
       </c>
       <c r="M32" s="16">
         <v>382231</v>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="AS32" s="10">
         <f t="shared" si="16"/>
-        <v>82535</v>
+        <v>82536</v>
       </c>
       <c r="AT32" s="13">
-        <v>396003</v>
+        <v>396004</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="17"/>
-        <v>0.98367753506187683</v>
+        <v>0.98368001907723801</v>
       </c>
       <c r="AV32" s="18">
         <v>187080</v>
@@ -6223,14 +6223,14 @@
       </c>
       <c r="AX32" s="10">
         <f t="shared" si="18"/>
-        <v>44448</v>
+        <v>44449</v>
       </c>
       <c r="AY32" s="20">
-        <v>183820</v>
+        <v>183821</v>
       </c>
       <c r="AZ32" s="12">
         <f t="shared" si="19"/>
-        <v>0.98257429976480648</v>
+        <v>0.98257964507162709</v>
       </c>
       <c r="BA32" s="18">
         <v>189893</v>
@@ -6240,14 +6240,14 @@
       </c>
       <c r="BC32" s="10">
         <f t="shared" si="20"/>
-        <v>238146</v>
+        <v>49712</v>
       </c>
       <c r="BD32" s="20">
-        <v>376870</v>
+        <v>188436</v>
       </c>
       <c r="BE32" s="12">
         <f t="shared" si="21"/>
-        <v>1.9846439837171459</v>
+        <v>0.99232725798212673</v>
       </c>
       <c r="BF32" s="18">
         <v>410654</v>
@@ -6257,14 +6257,14 @@
       </c>
       <c r="BH32" s="10">
         <f t="shared" si="22"/>
-        <v>124579</v>
+        <v>124580</v>
       </c>
       <c r="BI32" s="11">
-        <v>404236</v>
+        <v>404237</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="23"/>
-        <v>0.98437127119180623</v>
+        <v>0.98437370633185117</v>
       </c>
       <c r="BK32" s="24"/>
       <c r="BL32" s="24"/>
@@ -6437,14 +6437,14 @@
       </c>
       <c r="AX33" s="10">
         <f t="shared" si="18"/>
-        <v>93001</v>
+        <v>93002</v>
       </c>
       <c r="AY33" s="20">
-        <v>564194</v>
+        <v>564195</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.98795252454147797</v>
+        <v>0.98795427562802718</v>
       </c>
       <c r="BA33" s="18">
         <v>575700</v>
@@ -6454,14 +6454,14 @@
       </c>
       <c r="BC33" s="10">
         <f t="shared" si="20"/>
-        <v>670804</v>
+        <v>96951</v>
       </c>
       <c r="BD33" s="20">
-        <v>1147710</v>
+        <v>573857</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>1.9935904116727463</v>
+        <v>0.99679867986798676</v>
       </c>
       <c r="BF33" s="18">
         <v>986775</v>
@@ -6471,14 +6471,14 @@
       </c>
       <c r="BH33" s="10">
         <f t="shared" si="22"/>
-        <v>171038</v>
+        <v>171039</v>
       </c>
       <c r="BI33" s="11">
-        <v>975802</v>
+        <v>975803</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.98887993716906086</v>
+        <v>0.98888095057130554</v>
       </c>
       <c r="BK33" s="24"/>
       <c r="BL33" s="24"/>
@@ -6858,14 +6858,14 @@
       </c>
       <c r="BC35" s="10">
         <f t="shared" si="20"/>
-        <v>13651</v>
+        <v>2551</v>
       </c>
       <c r="BD35" s="20">
-        <v>22200</v>
+        <v>11100</v>
       </c>
       <c r="BE35" s="12">
         <f t="shared" si="21"/>
-        <v>1.9285900443054469</v>
+        <v>0.96429502215272345</v>
       </c>
       <c r="BF35" s="18">
         <v>14581</v>
@@ -6902,14 +6902,14 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" si="0"/>
-        <v>551058</v>
+        <v>551060</v>
       </c>
       <c r="F36" s="20">
-        <v>726065</v>
+        <v>726067</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.97116071404686299</v>
+        <v>0.97116338918122158</v>
       </c>
       <c r="H36" s="15">
         <v>754952</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v>545540</v>
+        <v>545543</v>
       </c>
       <c r="K36" s="20">
-        <v>731890</v>
+        <v>731893</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.96945236253430678</v>
+        <v>0.96945633629687711</v>
       </c>
       <c r="M36" s="16">
         <v>1378095</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="O36" s="10">
         <f t="shared" si="4"/>
-        <v>493444</v>
+        <v>493448</v>
       </c>
       <c r="P36" s="13">
-        <v>1346555</v>
+        <v>1346559</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.97711333398640876</v>
+        <v>0.97711623654392477</v>
       </c>
       <c r="R36" s="16">
         <v>758000</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="T36" s="10">
         <f t="shared" si="6"/>
-        <v>231304</v>
+        <v>231309</v>
       </c>
       <c r="U36" s="20">
-        <v>732476</v>
+        <v>732481</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.96632717678100266</v>
+        <v>0.96633377308707125</v>
       </c>
       <c r="W36" s="16">
         <v>766789</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="8"/>
-        <v>245544</v>
+        <v>245549</v>
       </c>
       <c r="Z36" s="20">
-        <v>748542</v>
+        <v>748547</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="9"/>
-        <v>0.97620336233305383</v>
+        <v>0.97620988303170753</v>
       </c>
       <c r="AB36" s="17">
         <v>1410553</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="AD36" s="10">
         <f t="shared" si="10"/>
-        <v>344797</v>
+        <v>344803</v>
       </c>
       <c r="AE36" s="11">
-        <v>1378474</v>
+        <v>1378480</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.9772578556069853</v>
+        <v>0.97726210925785839</v>
       </c>
       <c r="AG36" s="16">
         <v>767229</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="AI36" s="10">
         <f t="shared" si="12"/>
-        <v>202706</v>
+        <v>202711</v>
       </c>
       <c r="AJ36" s="20">
-        <v>744524</v>
+        <v>744529</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.97040648880581937</v>
+        <v>0.97041300576490197</v>
       </c>
       <c r="AL36" s="18">
         <v>779513</v>
@@ -7021,14 +7021,14 @@
       </c>
       <c r="AN36" s="10">
         <f t="shared" si="14"/>
-        <v>205112</v>
+        <v>205116</v>
       </c>
       <c r="AO36" s="11">
-        <v>755710</v>
+        <v>755714</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.96946426807506736</v>
+        <v>0.96946939948403688</v>
       </c>
       <c r="AQ36" s="11">
         <v>1443943</v>
@@ -7038,14 +7038,14 @@
       </c>
       <c r="AS36" s="10">
         <f t="shared" si="16"/>
-        <v>324145</v>
+        <v>324150</v>
       </c>
       <c r="AT36" s="13">
-        <v>1402891</v>
+        <v>1402896</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.97156951486312138</v>
+        <v>0.97157297760368655</v>
       </c>
       <c r="AV36" s="18">
         <v>783108</v>
@@ -7055,14 +7055,14 @@
       </c>
       <c r="AX36" s="10">
         <f t="shared" si="18"/>
-        <v>207951</v>
+        <v>207956</v>
       </c>
       <c r="AY36" s="20">
-        <v>758548</v>
+        <v>758553</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.96863778686975488</v>
+        <v>0.96864417168513151</v>
       </c>
       <c r="BA36" s="18">
         <v>793830</v>
@@ -7072,14 +7072,14 @@
       </c>
       <c r="BC36" s="10">
         <f t="shared" si="20"/>
-        <v>978512</v>
+        <v>206330</v>
       </c>
       <c r="BD36" s="20">
-        <v>1544375</v>
+        <v>772193</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>1.9454732121486968</v>
+        <v>0.97274353450990769</v>
       </c>
       <c r="BF36" s="18">
         <v>1468416</v>
@@ -7089,14 +7089,14 @@
       </c>
       <c r="BH36" s="10">
         <f t="shared" si="24"/>
-        <v>383749</v>
+        <v>383755</v>
       </c>
       <c r="BI36" s="11">
-        <v>1426415</v>
+        <v>1426421</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="25"/>
-        <v>0.97139707004009768</v>
+        <v>0.97140115607566246</v>
       </c>
       <c r="BK36" s="24"/>
       <c r="BL36" s="24"/>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" si="0"/>
-        <v>478360</v>
+        <v>478362</v>
       </c>
       <c r="F37" s="20">
-        <v>566443</v>
+        <v>566445</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.95615588344021185</v>
+        <v>0.95615925944056301</v>
       </c>
       <c r="H37" s="15">
         <v>593173</v>
@@ -7133,14 +7133,14 @@
       </c>
       <c r="J37" s="10">
         <f t="shared" si="2"/>
-        <v>459865</v>
+        <v>459867</v>
       </c>
       <c r="K37" s="20">
-        <v>566666</v>
+        <v>566668</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.95531320542236409</v>
+        <v>0.95531657711999707</v>
       </c>
       <c r="M37" s="16">
         <v>768378</v>
@@ -7150,14 +7150,14 @@
       </c>
       <c r="O37" s="10">
         <f t="shared" si="4"/>
-        <v>267464</v>
+        <v>267466</v>
       </c>
       <c r="P37" s="13">
-        <v>738207</v>
+        <v>738209</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.960734169900752</v>
+        <v>0.96073677278631087</v>
       </c>
       <c r="R37" s="16">
         <v>601605</v>
@@ -7167,14 +7167,14 @@
       </c>
       <c r="T37" s="10">
         <f t="shared" si="6"/>
-        <v>144760</v>
+        <v>144762</v>
       </c>
       <c r="U37" s="20">
-        <v>573946</v>
+        <v>573948</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.95402465072597464</v>
+        <v>0.95402797516642979</v>
       </c>
       <c r="W37" s="16">
         <v>609453</v>
@@ -7184,14 +7184,14 @@
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="8"/>
-        <v>142443</v>
+        <v>142446</v>
       </c>
       <c r="Z37" s="20">
-        <v>583179</v>
+        <v>583182</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.95688921048874975</v>
+        <v>0.95689413293559966</v>
       </c>
       <c r="AB37" s="17">
         <v>790568</v>
@@ -7201,14 +7201,14 @@
       </c>
       <c r="AD37" s="10">
         <f t="shared" si="10"/>
-        <v>172697</v>
+        <v>172702</v>
       </c>
       <c r="AE37" s="11">
-        <v>759629</v>
+        <v>759634</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.96086484654071502</v>
+        <v>0.96087117110735576</v>
       </c>
       <c r="AG37" s="16">
         <v>617773</v>
@@ -7218,14 +7218,14 @@
       </c>
       <c r="AI37" s="10">
         <f t="shared" si="12"/>
-        <v>117973</v>
+        <v>117976</v>
       </c>
       <c r="AJ37" s="20">
-        <v>589775</v>
+        <v>589778</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.95467914589986935</v>
+        <v>0.9546840020525339</v>
       </c>
       <c r="AL37" s="18">
         <v>624724</v>
@@ -7235,14 +7235,14 @@
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="14"/>
-        <v>122527</v>
+        <v>122530</v>
       </c>
       <c r="AO37" s="11">
-        <v>596616</v>
+        <v>596619</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.9550073312374745</v>
+        <v>0.95501213335809099</v>
       </c>
       <c r="AQ37" s="11">
         <v>810789</v>
@@ -7252,14 +7252,14 @@
       </c>
       <c r="AS37" s="10">
         <f t="shared" si="16"/>
-        <v>156914</v>
+        <v>156919</v>
       </c>
       <c r="AT37" s="13">
-        <v>777522</v>
+        <v>777527</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.95896959628213996</v>
+        <v>0.95897576311469446</v>
       </c>
       <c r="AV37" s="18">
         <v>633338</v>
@@ -7269,14 +7269,14 @@
       </c>
       <c r="AX37" s="10">
         <f t="shared" si="18"/>
-        <v>130846</v>
+        <v>130849</v>
       </c>
       <c r="AY37" s="20">
-        <v>605832</v>
+        <v>605835</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.95656979369625694</v>
+        <v>0.95657453050345942</v>
       </c>
       <c r="BA37" s="18">
         <v>640933</v>
@@ -7286,14 +7286,14 @@
       </c>
       <c r="BC37" s="10">
         <f t="shared" si="20"/>
-        <v>746417</v>
+        <v>131375</v>
       </c>
       <c r="BD37" s="20">
-        <v>1230094</v>
+        <v>615052</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>1.9192240062533836</v>
+        <v>0.95961980425411075</v>
       </c>
       <c r="BF37" s="18">
         <v>830528</v>
@@ -7303,14 +7303,14 @@
       </c>
       <c r="BH37" s="10">
         <f t="shared" si="24"/>
-        <v>185612</v>
+        <v>185616</v>
       </c>
       <c r="BI37" s="11">
-        <v>797120</v>
+        <v>797124</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="25"/>
-        <v>0.9597749865146028</v>
+        <v>0.9597798027279032</v>
       </c>
       <c r="BK37" s="24"/>
       <c r="BL37" s="24"/>
@@ -7500,14 +7500,14 @@
       </c>
       <c r="BC38" s="10">
         <f t="shared" si="20"/>
-        <v>27729</v>
+        <v>6725</v>
       </c>
       <c r="BD38" s="20">
-        <v>42008</v>
+        <v>21004</v>
       </c>
       <c r="BE38" s="12">
         <f t="shared" si="21"/>
-        <v>1.6959909564374824</v>
+        <v>0.84799547821874122</v>
       </c>
       <c r="BF38" s="18">
         <v>37269</v>
@@ -7714,14 +7714,14 @@
       </c>
       <c r="BC39" s="10">
         <f t="shared" si="20"/>
-        <v>219</v>
+        <v>46</v>
       </c>
       <c r="BD39" s="20">
-        <v>346</v>
+        <v>173</v>
       </c>
       <c r="BE39" s="12">
         <f t="shared" si="21"/>
-        <v>2.0116279069767442</v>
+        <v>1.0058139534883721</v>
       </c>
       <c r="BF39" s="18">
         <v>228</v>
@@ -7758,14 +7758,14 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="0"/>
-        <v>228460</v>
+        <v>228461</v>
       </c>
       <c r="F40" s="20">
-        <v>243745</v>
+        <v>243746</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.95566411686982711</v>
+        <v>0.95566803762355279</v>
       </c>
       <c r="H40" s="15">
         <v>254802</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="2"/>
-        <v>221640</v>
+        <v>221641</v>
       </c>
       <c r="K40" s="20">
-        <v>243978</v>
+        <v>243979</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="3"/>
-        <v>0.95751995667223966</v>
+        <v>0.95752388128821597</v>
       </c>
       <c r="M40" s="16">
         <v>315837</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="O40" s="10">
         <f t="shared" si="4"/>
-        <v>162873</v>
+        <v>162874</v>
       </c>
       <c r="P40" s="13">
-        <v>303398</v>
+        <v>303399</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.96061576066135379</v>
+        <v>0.96061892685150885</v>
       </c>
       <c r="R40" s="16">
         <v>257348</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="T40" s="10">
         <f t="shared" si="6"/>
-        <v>76828</v>
+        <v>76829</v>
       </c>
       <c r="U40" s="20">
-        <v>245527</v>
+        <v>245528</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="7"/>
-        <v>0.95406608949748983</v>
+        <v>0.9540699752863826</v>
       </c>
       <c r="W40" s="16">
         <v>259512</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="Y40" s="10">
         <f t="shared" si="8"/>
-        <v>69285</v>
+        <v>69287</v>
       </c>
       <c r="Z40" s="20">
-        <v>247807</v>
+        <v>247809</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="9"/>
-        <v>0.95489611270384411</v>
+        <v>0.954903819476556</v>
       </c>
       <c r="AB40" s="17">
         <v>322067</v>
@@ -7843,14 +7843,14 @@
       </c>
       <c r="AD40" s="10">
         <f t="shared" si="10"/>
-        <v>74967</v>
+        <v>74968</v>
       </c>
       <c r="AE40" s="11">
-        <v>309033</v>
+        <v>309034</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.95953015987356671</v>
+        <v>0.95953326481756906</v>
       </c>
       <c r="AG40" s="16">
         <v>262041</v>
@@ -7860,14 +7860,14 @@
       </c>
       <c r="AI40" s="10">
         <f t="shared" si="12"/>
-        <v>51917</v>
+        <v>51918</v>
       </c>
       <c r="AJ40" s="20">
-        <v>250270</v>
+        <v>250271</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="13"/>
-        <v>0.95507954862025413</v>
+        <v>0.9550833648169561</v>
       </c>
       <c r="AL40" s="18">
         <v>264607</v>
@@ -7877,14 +7877,14 @@
       </c>
       <c r="AN40" s="10">
         <f t="shared" si="14"/>
-        <v>57108</v>
+        <v>57110</v>
       </c>
       <c r="AO40" s="11">
-        <v>252877</v>
+        <v>252879</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="15"/>
-        <v>0.95567010698885513</v>
+        <v>0.95567766536788523</v>
       </c>
       <c r="AQ40" s="11">
         <v>328683</v>
@@ -7894,14 +7894,14 @@
       </c>
       <c r="AS40" s="10">
         <f t="shared" si="16"/>
-        <v>67752</v>
+        <v>67755</v>
       </c>
       <c r="AT40" s="13">
-        <v>316044</v>
+        <v>316047</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.96154653571982729</v>
+        <v>0.96155566305528428</v>
       </c>
       <c r="AV40" s="18">
         <v>267796</v>
@@ -7911,14 +7911,14 @@
       </c>
       <c r="AX40" s="10">
         <f t="shared" si="18"/>
-        <v>56490</v>
+        <v>56493</v>
       </c>
       <c r="AY40" s="20">
-        <v>256127</v>
+        <v>256130</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="19"/>
-        <v>0.95642578679293189</v>
+        <v>0.95643698935010235</v>
       </c>
       <c r="BA40" s="18">
         <v>270158</v>
@@ -7928,14 +7928,14 @@
       </c>
       <c r="BC40" s="10">
         <f t="shared" si="20"/>
-        <v>316582</v>
+        <v>57703</v>
       </c>
       <c r="BD40" s="20">
-        <v>517765</v>
+        <v>258886</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="21"/>
-        <v>1.9165266251600914</v>
+        <v>0.95827626796171128</v>
       </c>
       <c r="BF40" s="18">
         <v>335514</v>
@@ -7945,14 +7945,14 @@
       </c>
       <c r="BH40" s="10">
         <f t="shared" si="24"/>
-        <v>84612</v>
+        <v>84617</v>
       </c>
       <c r="BI40" s="11">
-        <v>321800</v>
+        <v>321805</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="25"/>
-        <v>0.95912540162258508</v>
+        <v>0.9591403041303791</v>
       </c>
       <c r="BK40" s="24"/>
       <c r="BL40" s="24"/>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" si="0"/>
-        <v>641269</v>
+        <v>641279</v>
       </c>
       <c r="F41" s="20">
-        <v>777388</v>
+        <v>777398</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.96795513519705545</v>
+        <v>0.96796758657442683</v>
       </c>
       <c r="H41" s="15">
         <v>805681</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="J41" s="10">
         <f t="shared" si="2"/>
-        <v>648989</v>
+        <v>648998</v>
       </c>
       <c r="K41" s="20">
-        <v>778217</v>
+        <v>778226</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.96591206693468012</v>
+        <v>0.96592323760892962</v>
       </c>
       <c r="M41" s="16">
         <v>924274</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="O41" s="10">
         <f t="shared" si="4"/>
-        <v>314090</v>
+        <v>314099</v>
       </c>
       <c r="P41" s="13">
-        <v>890852</v>
+        <v>890861</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.96383972718046818</v>
+        <v>0.96384946455271925</v>
       </c>
       <c r="R41" s="16">
         <v>822173</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="T41" s="10">
         <f t="shared" si="6"/>
-        <v>171622</v>
+        <v>171634</v>
       </c>
       <c r="U41" s="20">
-        <v>791181</v>
+        <v>791193</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.96230477040720142</v>
+        <v>0.96231936587555178</v>
       </c>
       <c r="W41" s="16">
         <v>833879</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="8"/>
-        <v>179595</v>
+        <v>179608</v>
       </c>
       <c r="Z41" s="20">
-        <v>799934</v>
+        <v>799947</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.9592926551693951</v>
+        <v>0.95930824496119937</v>
       </c>
       <c r="AB41" s="17">
         <v>956956</v>
@@ -8057,14 +8057,14 @@
       </c>
       <c r="AD41" s="10">
         <f t="shared" si="10"/>
-        <v>182771</v>
+        <v>182784</v>
       </c>
       <c r="AE41" s="11">
-        <v>915498</v>
+        <v>915511</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.95667721399938976</v>
+        <v>0.95669079874100793</v>
       </c>
       <c r="AG41" s="16">
         <v>851169</v>
@@ -8074,14 +8074,14 @@
       </c>
       <c r="AI41" s="10">
         <f t="shared" si="12"/>
-        <v>150969</v>
+        <v>150982</v>
       </c>
       <c r="AJ41" s="20">
-        <v>811578</v>
+        <v>811591</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.95348632292764424</v>
+        <v>0.95350159604026929</v>
       </c>
       <c r="AL41" s="18">
         <v>859964</v>
@@ -8091,14 +8091,14 @@
       </c>
       <c r="AN41" s="10">
         <f t="shared" si="14"/>
-        <v>152871</v>
+        <v>152884</v>
       </c>
       <c r="AO41" s="11">
-        <v>818587</v>
+        <v>818600</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.95188519519421744</v>
+        <v>0.95190031210608816</v>
       </c>
       <c r="AQ41" s="11">
         <v>982238</v>
@@ -8108,14 +8108,14 @@
       </c>
       <c r="AS41" s="10">
         <f t="shared" si="16"/>
-        <v>184975</v>
+        <v>184992</v>
       </c>
       <c r="AT41" s="13">
-        <v>934400</v>
+        <v>934417</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.95129693618043687</v>
+        <v>0.9513142435947296</v>
       </c>
       <c r="AV41" s="18">
         <v>867973</v>
@@ -8125,14 +8125,14 @@
       </c>
       <c r="AX41" s="10">
         <f t="shared" si="18"/>
-        <v>169830</v>
+        <v>169843</v>
       </c>
       <c r="AY41" s="20">
-        <v>827394</v>
+        <v>827407</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.95324854574969498</v>
+        <v>0.9532635231741079</v>
       </c>
       <c r="BA41" s="18">
         <v>869274</v>
@@ -8142,14 +8142,14 @@
       </c>
       <c r="BC41" s="10">
         <f t="shared" si="20"/>
-        <v>987782</v>
+        <v>154245</v>
       </c>
       <c r="BD41" s="20">
-        <v>1667116</v>
+        <v>833579</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>1.9178256798201718</v>
+        <v>0.95893699800063037</v>
       </c>
       <c r="BF41" s="18">
         <v>986817</v>
@@ -8159,14 +8159,14 @@
       </c>
       <c r="BH41" s="10">
         <f t="shared" si="24"/>
-        <v>196739</v>
+        <v>196752</v>
       </c>
       <c r="BI41" s="11">
-        <v>950345</v>
+        <v>950358</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="25"/>
-        <v>0.96304076642376446</v>
+        <v>0.96305394009223599</v>
       </c>
       <c r="BK41" s="24"/>
       <c r="BL41" s="24"/>
@@ -8356,14 +8356,14 @@
       </c>
       <c r="BC42" s="10">
         <f t="shared" si="20"/>
-        <v>20826</v>
+        <v>3739</v>
       </c>
       <c r="BD42" s="20">
-        <v>34174</v>
+        <v>17087</v>
       </c>
       <c r="BE42" s="12">
         <f t="shared" si="21"/>
-        <v>1.9135449913209026</v>
+        <v>0.95677249566045131</v>
       </c>
       <c r="BF42" s="18">
         <v>20264</v>
@@ -8373,14 +8373,14 @@
       </c>
       <c r="BH42" s="10">
         <f t="shared" si="24"/>
-        <v>4732</v>
+        <v>4733</v>
       </c>
       <c r="BI42" s="11">
-        <v>19410</v>
+        <v>19411</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="25"/>
-        <v>0.95785629688116858</v>
+        <v>0.95790564547966839</v>
       </c>
       <c r="BK42" s="24"/>
       <c r="BL42" s="24"/>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="E43" s="10">
         <f t="shared" si="0"/>
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="F43" s="20">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="G43" s="12">
         <f t="shared" si="1"/>
-        <v>0.9106395696353855</v>
+        <v>0.91093843395098628</v>
       </c>
       <c r="H43" s="15">
         <v>3343</v>
@@ -8417,14 +8417,14 @@
       </c>
       <c r="J43" s="10">
         <f t="shared" si="2"/>
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="K43" s="20">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="L43" s="12">
         <f t="shared" si="3"/>
-        <v>0.90637152258450493</v>
+        <v>0.90667065510020939</v>
       </c>
       <c r="M43" s="16">
         <v>4020</v>
@@ -8434,14 +8434,14 @@
       </c>
       <c r="O43" s="10">
         <f t="shared" si="4"/>
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="P43" s="13">
-        <v>3690</v>
+        <v>3691</v>
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="5"/>
-        <v>0.91791044776119401</v>
+        <v>0.91815920398009954</v>
       </c>
       <c r="R43" s="16">
         <v>3295</v>
@@ -8451,14 +8451,14 @@
       </c>
       <c r="T43" s="10">
         <f t="shared" si="6"/>
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="U43" s="20">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="7"/>
-        <v>0.91016691957511386</v>
+        <v>0.91047040971168436</v>
       </c>
       <c r="W43" s="16">
         <v>3265</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="Y43" s="10">
         <f t="shared" si="8"/>
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="Z43" s="20">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="AA43" s="12">
         <f t="shared" si="9"/>
-        <v>0.92312404287901995</v>
+        <v>0.92343032159264926</v>
       </c>
       <c r="AB43" s="17">
         <v>4071</v>
@@ -8485,14 +8485,14 @@
       </c>
       <c r="AD43" s="10">
         <f t="shared" si="10"/>
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="AE43" s="11">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="AF43" s="12">
         <f t="shared" si="11"/>
-        <v>0.93146647015475315</v>
+        <v>0.93171211004667154</v>
       </c>
       <c r="AG43" s="16">
         <v>3330</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="AI43" s="10">
         <f t="shared" si="12"/>
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AJ43" s="20">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="AK43" s="12">
         <f t="shared" si="13"/>
-        <v>0.91561561561561566</v>
+        <v>0.91591591591591592</v>
       </c>
       <c r="AL43" s="18">
         <v>3339</v>
@@ -8519,14 +8519,14 @@
       </c>
       <c r="AN43" s="10">
         <f t="shared" si="14"/>
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AO43" s="11">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="AP43" s="12">
         <f t="shared" si="15"/>
-        <v>0.91943695717280627</v>
+        <v>0.91973644803833488</v>
       </c>
       <c r="AQ43" s="11">
         <v>4111</v>
@@ -8536,14 +8536,14 @@
       </c>
       <c r="AS43" s="10">
         <f t="shared" si="16"/>
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="AT43" s="13">
-        <v>3856</v>
+        <v>3857</v>
       </c>
       <c r="AU43" s="12">
         <f t="shared" si="17"/>
-        <v>0.93797129652152766</v>
+        <v>0.93821454633909029</v>
       </c>
       <c r="AV43" s="18">
         <v>3256</v>
@@ -8553,14 +8553,14 @@
       </c>
       <c r="AX43" s="10">
         <f t="shared" si="18"/>
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="AY43" s="20">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="AZ43" s="12">
         <f t="shared" si="19"/>
-        <v>0.95362407862407861</v>
+        <v>0.9539312039312039</v>
       </c>
       <c r="BA43" s="18">
         <v>3286</v>
@@ -8570,14 +8570,14 @@
       </c>
       <c r="BC43" s="10">
         <f t="shared" si="20"/>
-        <v>4219</v>
+        <v>1094</v>
       </c>
       <c r="BD43" s="20">
-        <v>6252</v>
+        <v>3127</v>
       </c>
       <c r="BE43" s="12">
         <f t="shared" si="21"/>
-        <v>1.9026171637248934</v>
+        <v>0.95161290322580649</v>
       </c>
       <c r="BF43" s="18">
         <v>4091</v>
@@ -8587,14 +8587,14 @@
       </c>
       <c r="BH43" s="10">
         <f t="shared" si="24"/>
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="BI43" s="11">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="BJ43" s="12">
         <f t="shared" si="25"/>
-        <v>0.96088975800537768</v>
+        <v>0.96113419701784408</v>
       </c>
       <c r="BK43" s="24"/>
       <c r="BL43" s="24"/>
@@ -8750,14 +8750,14 @@
       </c>
       <c r="AS44" s="10">
         <f t="shared" si="16"/>
-        <v>90447</v>
+        <v>90448</v>
       </c>
       <c r="AT44" s="13">
-        <v>359866</v>
+        <v>359867</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="17"/>
-        <v>0.8860268319886152</v>
+        <v>0.88602929409070874</v>
       </c>
       <c r="AV44" s="18">
         <v>341214</v>
@@ -8767,14 +8767,14 @@
       </c>
       <c r="AX44" s="10">
         <f t="shared" si="18"/>
-        <v>79996</v>
+        <v>79997</v>
       </c>
       <c r="AY44" s="20">
-        <v>298441</v>
+        <v>298442</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="19"/>
-        <v>0.87464465115733825</v>
+        <v>0.87464758186944269</v>
       </c>
       <c r="BA44" s="18">
         <v>343859</v>
@@ -8784,14 +8784,14 @@
       </c>
       <c r="BC44" s="10">
         <f t="shared" si="20"/>
-        <v>381791</v>
+        <v>79459</v>
       </c>
       <c r="BD44" s="20">
-        <v>604669</v>
+        <v>302337</v>
       </c>
       <c r="BE44" s="12">
         <f t="shared" si="21"/>
-        <v>1.7584794930480225</v>
+        <v>0.87924701694589935</v>
       </c>
       <c r="BF44" s="18">
         <v>410714</v>
@@ -8801,14 +8801,14 @@
       </c>
       <c r="BH44" s="10">
         <f t="shared" si="24"/>
-        <v>103157</v>
+        <v>103159</v>
       </c>
       <c r="BI44" s="11">
-        <v>367435</v>
+        <v>367437</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="25"/>
-        <v>0.89462497017389231</v>
+        <v>0.89462983974249721</v>
       </c>
       <c r="BK44" s="24"/>
       <c r="BL44" s="24"/>
@@ -8845,14 +8845,14 @@
       </c>
       <c r="J45" s="10">
         <f t="shared" si="2"/>
-        <v>171222</v>
+        <v>171223</v>
       </c>
       <c r="K45" s="20">
-        <v>220016</v>
+        <v>220017</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="3"/>
-        <v>0.9217646319493904</v>
+        <v>0.92176882148393313</v>
       </c>
       <c r="M45" s="16">
         <v>292586</v>
@@ -8862,14 +8862,14 @@
       </c>
       <c r="O45" s="10">
         <f t="shared" si="4"/>
-        <v>100447</v>
+        <v>100448</v>
       </c>
       <c r="P45" s="13">
-        <v>272785</v>
+        <v>272786</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>0.93232417135474699</v>
+        <v>0.93232758915327463</v>
       </c>
       <c r="R45" s="16">
         <v>242899</v>
@@ -8879,14 +8879,14 @@
       </c>
       <c r="T45" s="10">
         <f t="shared" si="6"/>
-        <v>58711</v>
+        <v>58712</v>
       </c>
       <c r="U45" s="20">
-        <v>223286</v>
+        <v>223287</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="7"/>
-        <v>0.91925450495885119</v>
+        <v>0.91925862189634377</v>
       </c>
       <c r="W45" s="16">
         <v>244806</v>
@@ -8896,14 +8896,14 @@
       </c>
       <c r="Y45" s="10">
         <f t="shared" si="8"/>
-        <v>58460</v>
+        <v>58461</v>
       </c>
       <c r="Z45" s="20">
-        <v>225569</v>
+        <v>225570</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="9"/>
-        <v>0.92141940965499214</v>
+        <v>0.92142349452219308</v>
       </c>
       <c r="AB45" s="17">
         <v>299772</v>
@@ -8913,14 +8913,14 @@
       </c>
       <c r="AD45" s="10">
         <f t="shared" si="10"/>
-        <v>63876</v>
+        <v>63877</v>
       </c>
       <c r="AE45" s="11">
-        <v>277631</v>
+        <v>277632</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="11"/>
-        <v>0.92614053347210545</v>
+        <v>0.92614386934069892</v>
       </c>
       <c r="AG45" s="16">
         <v>246243</v>
@@ -8930,14 +8930,14 @@
       </c>
       <c r="AI45" s="10">
         <f t="shared" si="12"/>
-        <v>48117</v>
+        <v>48118</v>
       </c>
       <c r="AJ45" s="20">
-        <v>227311</v>
+        <v>227312</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="13"/>
-        <v>0.92311659620781095</v>
+        <v>0.92312065723695702</v>
       </c>
       <c r="AL45" s="18">
         <v>247584</v>
@@ -8947,14 +8947,14 @@
       </c>
       <c r="AN45" s="10">
         <f t="shared" si="14"/>
-        <v>51423</v>
+        <v>51424</v>
       </c>
       <c r="AO45" s="11">
-        <v>229461</v>
+        <v>229462</v>
       </c>
       <c r="AP45" s="12">
         <f t="shared" si="15"/>
-        <v>0.92680060100814265</v>
+        <v>0.92680464004135965</v>
       </c>
       <c r="AQ45" s="11">
         <v>303759</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="AS45" s="10">
         <f t="shared" si="16"/>
-        <v>67570</v>
+        <v>67572</v>
       </c>
       <c r="AT45" s="13">
-        <v>282321</v>
+        <v>282323</v>
       </c>
       <c r="AU45" s="12">
         <f t="shared" si="17"/>
-        <v>0.92942431335367837</v>
+        <v>0.92943089752073194</v>
       </c>
       <c r="AV45" s="18">
         <v>248547</v>
@@ -8981,14 +8981,14 @@
       </c>
       <c r="AX45" s="10">
         <f t="shared" si="18"/>
-        <v>55334</v>
+        <v>55336</v>
       </c>
       <c r="AY45" s="20">
-        <v>230987</v>
+        <v>230989</v>
       </c>
       <c r="AZ45" s="12">
         <f t="shared" si="19"/>
-        <v>0.92934937858835553</v>
+        <v>0.92935742535617005</v>
       </c>
       <c r="BA45" s="18">
         <v>248925</v>
@@ -8998,14 +8998,14 @@
       </c>
       <c r="BC45" s="10">
         <f t="shared" si="20"/>
-        <v>285072</v>
+        <v>51927</v>
       </c>
       <c r="BD45" s="20">
-        <v>466298</v>
+        <v>233153</v>
       </c>
       <c r="BE45" s="12">
         <f t="shared" si="21"/>
-        <v>1.8732469619363261</v>
+        <v>0.93663955006528066</v>
       </c>
       <c r="BF45" s="18">
         <v>305535</v>
@@ -9015,14 +9015,14 @@
       </c>
       <c r="BH45" s="10">
         <f t="shared" si="24"/>
-        <v>79704</v>
+        <v>79707</v>
       </c>
       <c r="BI45" s="11">
-        <v>287205</v>
+        <v>287208</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="25"/>
-        <v>0.94000687318965093</v>
+        <v>0.94001669203200944</v>
       </c>
       <c r="BK45" s="24"/>
       <c r="BL45" s="24"/>
@@ -9212,14 +9212,14 @@
       </c>
       <c r="BC46" s="10">
         <f t="shared" si="20"/>
-        <v>2995</v>
+        <v>735</v>
       </c>
       <c r="BD46" s="20">
-        <v>4520</v>
+        <v>2260</v>
       </c>
       <c r="BE46" s="12">
         <f t="shared" si="21"/>
-        <v>1.946597760551249</v>
+        <v>0.9732988802756245</v>
       </c>
       <c r="BF46" s="18">
         <v>5417</v>
@@ -9426,14 +9426,14 @@
       </c>
       <c r="BC47" s="10">
         <f t="shared" si="20"/>
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="BD47" s="20">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="BE47" s="12">
         <f t="shared" si="21"/>
-        <v>1.6296296296296295</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="BF47" s="18">
         <v>89</v>
@@ -9456,10 +9456,10 @@
       <c r="BL47" s="24"/>
     </row>
     <row r="48" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="26"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="6">
         <f>SUM(C10:C47)</f>
         <v>6932700</v>
@@ -9470,15 +9470,15 @@
       </c>
       <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v>5340441</v>
+        <v>5340469</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6558241</v>
+        <v>6558269</v>
       </c>
       <c r="G48" s="9">
         <f t="shared" si="1"/>
-        <v>0.94598655646429242</v>
+        <v>0.94599059529476248</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9490,15 +9490,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" si="2"/>
-        <v>5126266</v>
+        <v>5126294</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>6572707</v>
+        <v>6572735</v>
       </c>
       <c r="L48" s="9">
         <f t="shared" si="3"/>
-        <v>0.94561282557334203</v>
+        <v>0.9456168539225619</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9510,15 +9510,15 @@
       </c>
       <c r="O48" s="8">
         <f t="shared" si="4"/>
-        <v>3595437</v>
+        <v>3595467</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>10438892</v>
+        <v>10438922</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="5"/>
-        <v>0.9615557043484525</v>
+        <v>0.9615584677328356</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9530,15 +9530,15 @@
       </c>
       <c r="T48" s="8">
         <f t="shared" si="6"/>
-        <v>1738530</v>
+        <v>1738564</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>6647600</v>
+        <v>6647634</v>
       </c>
       <c r="V48" s="9">
         <f t="shared" si="7"/>
-        <v>0.94718229084292616</v>
+        <v>0.94718713532783627</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9550,15 +9550,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" si="8"/>
-        <v>1753897</v>
+        <v>1753935</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>6780487</v>
+        <v>6780525</v>
       </c>
       <c r="AA48" s="9">
         <f t="shared" si="9"/>
-        <v>0.95153244660995306</v>
+        <v>0.95153777929962136</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9570,15 +9570,15 @@
       </c>
       <c r="AD48" s="8">
         <f t="shared" si="10"/>
-        <v>2305207</v>
+        <v>2305255</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>10747475</v>
+        <v>10747523</v>
       </c>
       <c r="AF48" s="9">
         <f t="shared" si="11"/>
-        <v>0.96121133211545329</v>
+        <v>0.96121562504415903</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9590,15 +9590,15 @@
       </c>
       <c r="AI48" s="8">
         <f t="shared" si="12"/>
-        <v>1483530</v>
+        <v>1483571</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6764609</v>
+        <v>6764650</v>
       </c>
       <c r="AK48" s="9">
         <f t="shared" si="13"/>
-        <v>0.94911509018868345</v>
+        <v>0.9491208427338339</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9610,15 +9610,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" si="14"/>
-        <v>1501389</v>
+        <v>1501432</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>6858753</v>
+        <v>6858796</v>
       </c>
       <c r="AP48" s="9">
         <f t="shared" si="15"/>
-        <v>0.95141148690066302</v>
+        <v>0.95141745164293279</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9630,15 +9630,15 @@
       </c>
       <c r="AS48" s="8">
         <f t="shared" si="16"/>
-        <v>2190552</v>
+        <v>2190616</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>10967038</v>
+        <v>10967102</v>
       </c>
       <c r="AU48" s="9">
         <f t="shared" si="17"/>
-        <v>0.95957085711070866</v>
+        <v>0.95957645684829096</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9650,15 +9650,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" si="18"/>
-        <v>1537234</v>
+        <v>1537282</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>6903570</v>
+        <v>6903618</v>
       </c>
       <c r="AZ48" s="9">
         <f t="shared" si="19"/>
-        <v>0.953167615797611</v>
+        <v>0.95317424309994281</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9670,15 +9670,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" si="20"/>
-        <v>8623892</v>
+        <v>1610408</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>14027116</v>
+        <v>7013632</v>
       </c>
       <c r="BE48" s="9">
         <f t="shared" si="21"/>
-        <v>1.9184374717919401</v>
+        <v>0.95922885660595147</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9690,15 +9690,15 @@
       </c>
       <c r="BH48" s="8">
         <f t="shared" si="24"/>
-        <v>2687980</v>
+        <v>2688047</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>11187849</v>
+        <v>11187916</v>
       </c>
       <c r="BJ48" s="9">
         <f t="shared" si="25"/>
-        <v>0.96188202995613437</v>
+        <v>0.9618877903213312</v>
       </c>
       <c r="BK48" s="24"/>
       <c r="BL48" s="24"/>
@@ -9796,6 +9796,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="AQ8:AU8"/>
+    <mergeCell ref="AV8:AZ8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="H8:L8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="M8:Q8"/>
@@ -9807,13 +9814,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="BA8:BE8"/>
-    <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="AV8:AZ8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="H8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
